--- a/results/scenario_base_case/heat_demand.xlsx
+++ b/results/scenario_base_case/heat_demand.xlsx
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>751.6750350997079</v>
+        <v>956.1900000000001</v>
       </c>
     </row>
     <row r="3">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>744.5875869245289</v>
+        <v>1114.3</v>
       </c>
     </row>
     <row r="4">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>758.7122572641963</v>
+        <v>1016.23</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>765.1621141370017</v>
+        <v>1001.62</v>
       </c>
     </row>
     <row r="6">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>767.5322702803611</v>
+        <v>1044.59</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>778.3506274440816</v>
+        <v>933.64</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>790.2455884480602</v>
+        <v>1074.09</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>801.8291946913249</v>
+        <v>886.02</v>
       </c>
     </row>
     <row r="10">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>806.2258308493391</v>
+        <v>1061.68</v>
       </c>
     </row>
     <row r="11">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>797.791814026442</v>
+        <v>959.7799999999999</v>
       </c>
     </row>
     <row r="12">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>825.9455857687688</v>
+        <v>968.2500000000001</v>
       </c>
     </row>
     <row r="13">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>815.5378727480066</v>
+        <v>1046.06</v>
       </c>
     </row>
     <row r="14">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>847.5232380280827</v>
+        <v>934.99</v>
       </c>
     </row>
     <row r="15">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>838.6241655506459</v>
+        <v>1074.88</v>
       </c>
     </row>
     <row r="16">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>841.3879913055731</v>
+        <v>934.1600000000001</v>
       </c>
     </row>
     <row r="17">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>852.607924026988</v>
+        <v>1049.03</v>
       </c>
     </row>
     <row r="18">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>865.6852890326329</v>
+        <v>959.7</v>
       </c>
     </row>
     <row r="19">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>874.1127950763665</v>
+        <v>985.58</v>
       </c>
     </row>
     <row r="20">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>880.8958643256491</v>
+        <v>1047.76</v>
       </c>
     </row>
     <row r="21">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>850.3554269642267</v>
+        <v>998.38</v>
       </c>
     </row>
     <row r="22">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>741.7846964946208</v>
+        <v>941.3200000000001</v>
       </c>
     </row>
     <row r="23">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>795.1844794992674</v>
+        <v>863.3600000000001</v>
       </c>
     </row>
     <row r="24">
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>738.3360762883846</v>
+        <v>956.4299999999998</v>
       </c>
     </row>
     <row r="25">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>697.6820736076963</v>
+        <v>828.62</v>
       </c>
     </row>
     <row r="26">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>587.2880924444689</v>
+        <v>632.4400000000001</v>
       </c>
     </row>
     <row r="27">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>591.9905026953429</v>
+        <v>735.99</v>
       </c>
     </row>
     <row r="28">
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>552.5335532694387</v>
+        <v>688.09</v>
       </c>
     </row>
     <row r="29">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>422.4279556607364</v>
+        <v>543.01</v>
       </c>
     </row>
     <row r="30">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>65.44867743027781</v>
+        <v>310.16</v>
       </c>
     </row>
     <row r="31">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>100.85</v>
       </c>
     </row>
     <row r="32">
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="33">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>211.24</v>
       </c>
     </row>
     <row r="34">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>134.1</v>
       </c>
     </row>
     <row r="35">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>82.72</v>
       </c>
     </row>
     <row r="36">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>33.21</v>
       </c>
     </row>
     <row r="37">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>114.12</v>
       </c>
     </row>
     <row r="38">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>85.95999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>94.94</v>
       </c>
     </row>
     <row r="42">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>431.5600000000001</v>
       </c>
     </row>
     <row r="43">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>527.27</v>
       </c>
     </row>
     <row r="44">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>465.69</v>
       </c>
     </row>
     <row r="45">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>274.98</v>
       </c>
     </row>
     <row r="46">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>258.28</v>
       </c>
     </row>
     <row r="47">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>232.02</v>
       </c>
     </row>
     <row r="48">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>199.31</v>
       </c>
     </row>
     <row r="49">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>418.9</v>
       </c>
     </row>
     <row r="50">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>624.84</v>
       </c>
     </row>
     <row r="51">
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>745.08</v>
       </c>
     </row>
     <row r="52">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>671.26</v>
       </c>
     </row>
     <row r="53">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>518.24</v>
       </c>
     </row>
     <row r="54">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>441.52</v>
       </c>
     </row>
     <row r="55">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>465.3699999999999</v>
       </c>
     </row>
     <row r="56">
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>632.1</v>
       </c>
     </row>
     <row r="57">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>202.15</v>
       </c>
     </row>
     <row r="58">
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>151.86</v>
       </c>
     </row>
     <row r="59">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>256.02</v>
       </c>
     </row>
     <row r="60">
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>354.75</v>
       </c>
     </row>
     <row r="61">
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>167.13</v>
       </c>
     </row>
     <row r="62">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>477.7400000000001</v>
       </c>
     </row>
     <row r="63">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>223.75</v>
       </c>
     </row>
     <row r="64">
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>432.83</v>
       </c>
     </row>
     <row r="65">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>300.59</v>
       </c>
     </row>
     <row r="66">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>199.33</v>
       </c>
     </row>
     <row r="67">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>58.12</v>
       </c>
     </row>
     <row r="68">
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>160.03</v>
       </c>
     </row>
     <row r="69">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>326.3</v>
       </c>
     </row>
     <row r="70">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>251.17</v>
       </c>
     </row>
     <row r="71">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>443.66</v>
       </c>
     </row>
     <row r="72">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>522.52</v>
       </c>
     </row>
     <row r="73">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>502.34</v>
       </c>
     </row>
     <row r="74">
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>52.34945480886964</v>
+        <v>937.88</v>
       </c>
     </row>
     <row r="75">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>164.9510551641951</v>
+        <v>1245.96</v>
       </c>
     </row>
     <row r="76">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>168.2422540313696</v>
+        <v>1378.36</v>
       </c>
     </row>
     <row r="77">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>95.64520613516842</v>
+        <v>1132.34</v>
       </c>
     </row>
     <row r="78">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>194.3797769834413</v>
+        <v>1074.09</v>
       </c>
     </row>
     <row r="79">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>292.7560224498917</v>
+        <v>1265.4</v>
       </c>
     </row>
     <row r="80">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>341.5494291963267</v>
+        <v>1199.43</v>
       </c>
     </row>
     <row r="81">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>350.9270439422842</v>
+        <v>845.5800000000002</v>
       </c>
     </row>
     <row r="82">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>397.6669974461009</v>
+        <v>1090.89</v>
       </c>
     </row>
     <row r="83">
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>508.4516253591414</v>
+        <v>1103.21</v>
       </c>
     </row>
     <row r="84">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>420.5063456961798</v>
+        <v>1006.7</v>
       </c>
     </row>
     <row r="85">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>487.5622554685455</v>
+        <v>997.1099999999999</v>
       </c>
     </row>
     <row r="86">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>480.3745877998136</v>
+        <v>1135.63</v>
       </c>
     </row>
     <row r="87">
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>494.0183905926872</v>
+        <v>962.05</v>
       </c>
     </row>
     <row r="88">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>490.2486494569918</v>
+        <v>1126.71</v>
       </c>
     </row>
     <row r="89">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>530.5138656104853</v>
+        <v>1013.54</v>
       </c>
     </row>
     <row r="90">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>520.6772409334973</v>
+        <v>1176.73</v>
       </c>
     </row>
     <row r="91">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>525.1992095904102</v>
+        <v>999.2400000000001</v>
       </c>
     </row>
     <row r="92">
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>538.5156132024882</v>
+        <v>1151.55</v>
       </c>
     </row>
     <row r="93">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>584.810740972738</v>
+        <v>983.84</v>
       </c>
     </row>
     <row r="94">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>650.5637973289118</v>
+        <v>1182.08</v>
       </c>
     </row>
     <row r="95">
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>664.8184507240229</v>
+        <v>1038.24</v>
       </c>
     </row>
     <row r="96">
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>692.0821059435616</v>
+        <v>1182.66</v>
       </c>
     </row>
     <row r="97">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>713.7641631973195</v>
+        <v>1162.02</v>
       </c>
     </row>
     <row r="98">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>731.0109846737361</v>
+        <v>1101.05</v>
       </c>
     </row>
     <row r="99">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>755.9581976780147</v>
+        <v>1230.8</v>
       </c>
     </row>
     <row r="100">
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>772.3872187859241</v>
+        <v>1033.41</v>
       </c>
     </row>
     <row r="101">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>787.3692192247346</v>
+        <v>1175.28</v>
       </c>
     </row>
     <row r="102">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>811.0163691467484</v>
+        <v>1021.56</v>
       </c>
     </row>
     <row r="103">
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>830.7096158938693</v>
+        <v>1099.98</v>
       </c>
     </row>
     <row r="104">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>835.7998825606288</v>
+        <v>1043.1</v>
       </c>
     </row>
     <row r="105">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>859.7397850171753</v>
+        <v>1016.41</v>
       </c>
     </row>
     <row r="106">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>871.6626493604264</v>
+        <v>1088.29</v>
       </c>
     </row>
     <row r="107">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>876.5550348461795</v>
+        <v>925.7699999999999</v>
       </c>
     </row>
     <row r="108">
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>895.0528560333073</v>
+        <v>1081.1</v>
       </c>
     </row>
     <row r="109">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>885.1976291301378</v>
+        <v>888.16</v>
       </c>
     </row>
     <row r="110">
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>915.3827639714921</v>
+        <v>1050.12</v>
       </c>
     </row>
     <row r="111">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>899.3943830962587</v>
+        <v>990.05</v>
       </c>
     </row>
     <row r="112">
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>911.3002729081192</v>
+        <v>956.4199999999998</v>
       </c>
     </row>
     <row r="113">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>908.6406196198088</v>
+        <v>951.21</v>
       </c>
     </row>
     <row r="114">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>932.8646710812785</v>
+        <v>950.5599999999999</v>
       </c>
     </row>
     <row r="115">
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>925.3672763466234</v>
+        <v>958.89</v>
       </c>
     </row>
     <row r="116">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>936.302362479633</v>
+        <v>928.65</v>
       </c>
     </row>
     <row r="117">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>946.8463368071749</v>
+        <v>917.6799999999998</v>
       </c>
     </row>
     <row r="118">
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>823.2375666923864</v>
+        <v>938.54</v>
       </c>
     </row>
     <row r="119">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>890.0514149965644</v>
+        <v>853.4800000000001</v>
       </c>
     </row>
     <row r="120">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>792.8589686987436</v>
+        <v>815.72</v>
       </c>
     </row>
     <row r="121">
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>761.416323367515</v>
+        <v>870.3099999999999</v>
       </c>
     </row>
     <row r="122">
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>620.5088780708285</v>
+        <v>614.85</v>
       </c>
     </row>
     <row r="123">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>623.2715411866192</v>
+        <v>636.78</v>
       </c>
     </row>
     <row r="124">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>625.67820419886</v>
+        <v>728.47</v>
       </c>
     </row>
     <row r="125">
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>527.8614206848204</v>
+        <v>547.55</v>
       </c>
     </row>
     <row r="126">
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>91.40738648317911</v>
+        <v>260.02</v>
       </c>
     </row>
     <row r="127">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>123.92</v>
       </c>
     </row>
     <row r="128">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="129">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>274.79</v>
       </c>
     </row>
     <row r="130">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>276.23</v>
       </c>
     </row>
     <row r="131">
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>77.06999999999999</v>
       </c>
     </row>
     <row r="132">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>24.61</v>
       </c>
     </row>
     <row r="133">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>269.76</v>
       </c>
     </row>
     <row r="134">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>22.41</v>
       </c>
     </row>
     <row r="135">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>23.22</v>
       </c>
     </row>
     <row r="137">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>245.34</v>
       </c>
     </row>
     <row r="138">
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>412.07</v>
       </c>
     </row>
     <row r="139">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>256.38</v>
       </c>
     </row>
     <row r="140">
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>178.18</v>
       </c>
     </row>
     <row r="141">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>285.17</v>
       </c>
     </row>
     <row r="142">
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>627.11</v>
       </c>
     </row>
     <row r="143">
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>692.5599999999999</v>
       </c>
     </row>
     <row r="144">
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>416.22</v>
       </c>
     </row>
     <row r="145">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>428.53</v>
       </c>
     </row>
     <row r="146">
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>725.85</v>
       </c>
     </row>
     <row r="147">
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>787.02</v>
       </c>
     </row>
     <row r="148">
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>528.95</v>
       </c>
     </row>
     <row r="149">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
     </row>
     <row r="150">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>0</v>
+        <v>549.24</v>
       </c>
     </row>
     <row r="151">
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>463.85</v>
       </c>
     </row>
     <row r="152">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>283.27</v>
       </c>
     </row>
     <row r="153">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>550.62</v>
       </c>
     </row>
     <row r="154">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>157.81</v>
       </c>
     </row>
     <row r="155">
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>0</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="156">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="157">
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>92.22</v>
       </c>
     </row>
     <row r="158">
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>431.82</v>
       </c>
     </row>
     <row r="159">
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>508.36</v>
       </c>
     </row>
     <row r="160">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>0</v>
+        <v>319.54</v>
       </c>
     </row>
     <row r="161">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>299.77</v>
       </c>
     </row>
     <row r="162">
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>0</v>
+        <v>259.44</v>
       </c>
     </row>
     <row r="163">
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>277.98</v>
       </c>
     </row>
     <row r="164">
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>283.4</v>
       </c>
     </row>
     <row r="165">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>72.67</v>
       </c>
     </row>
     <row r="166">
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>446.45</v>
       </c>
     </row>
     <row r="167">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>656.01</v>
       </c>
     </row>
     <row r="168">
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0</v>
+        <v>385.41</v>
       </c>
     </row>
     <row r="169">
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>0</v>
+        <v>421.54</v>
       </c>
     </row>
     <row r="170">
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>958.4200000000001</v>
       </c>
     </row>
     <row r="171">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>90.02896152312466</v>
+        <v>1372.85</v>
       </c>
     </row>
     <row r="172">
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>73.56831663070653</v>
+        <v>1370.77</v>
       </c>
     </row>
     <row r="173">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>1141.76</v>
       </c>
     </row>
     <row r="174">
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>11.44525218603918</v>
+        <v>994.2300000000001</v>
       </c>
     </row>
     <row r="175">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>100.1029971117548</v>
+        <v>1181.47</v>
       </c>
     </row>
     <row r="176">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>188.0566477764979</v>
+        <v>1150.34</v>
       </c>
     </row>
     <row r="177">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>211.5507943881682</v>
+        <v>969.0700000000001</v>
       </c>
     </row>
     <row r="178">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>290.9606750955427</v>
+        <v>953.8500000000001</v>
       </c>
     </row>
     <row r="179">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>320.7660919949658</v>
+        <v>1076.7</v>
       </c>
     </row>
     <row r="180">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>250.9191507118827</v>
+        <v>967.74</v>
       </c>
     </row>
     <row r="181">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>285.6178832083681</v>
+        <v>981.42</v>
       </c>
     </row>
     <row r="182">
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>326.6260257699882</v>
+        <v>1045.33</v>
       </c>
     </row>
     <row r="183">
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>319.1328165362239</v>
+        <v>975.02</v>
       </c>
     </row>
     <row r="184">
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>307.0755511088109</v>
+        <v>1044.39</v>
       </c>
     </row>
     <row r="185">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>333.8027646308385</v>
+        <v>1007.06</v>
       </c>
     </row>
     <row r="186">
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>460.6908746936109</v>
+        <v>1060.38</v>
       </c>
     </row>
     <row r="187">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>358.6499906693908</v>
+        <v>1067.9</v>
       </c>
     </row>
     <row r="188">
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>440.3944507625527</v>
+        <v>1016.97</v>
       </c>
     </row>
     <row r="189">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>405.3304170494266</v>
+        <v>1148.61</v>
       </c>
     </row>
     <row r="190">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>541.0989973634538</v>
+        <v>1128.76</v>
       </c>
     </row>
     <row r="191">
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>581.1095955460872</v>
+        <v>1074.11</v>
       </c>
     </row>
     <row r="192">
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>547.1151898384014</v>
+        <v>1190.9</v>
       </c>
     </row>
     <row r="193">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>605.8163747769687</v>
+        <v>1093.15</v>
       </c>
     </row>
     <row r="194">
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>47.94509820445541</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>41.07060110362794</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>102.3796875192407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>92.29987792501215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>85.20293791167077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>137.6363274281681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>98.52288691994659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>149.9430377354526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>191.3078701460875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>156.6272225666848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>247.5293051798292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>182.0672769945251</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>262.4928601527911</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>231.423876589296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>329.7253317008765</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>298.9652966269839</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>400.721132887038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>373.1465252583067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>434.1716037532955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>448.5709626117904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>302.0113040446554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>353.7364712780781</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>388.3126380955426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>323.5996133939406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>119.7795541087564</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>0.8414633407722975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>81.28412292464549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>87.10830750572927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>146.0321992367043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>177.9001797667646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>173.4352561950271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>109.9192664595037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>131.3741100612804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>160.7070278030194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>207.63585399404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>240.586390031668</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>215.7649066524648</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>224.8600131516508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>276.4705885816573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>272.4878493435106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>255.2696444658813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>316.6118726285605</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>311.0965241921741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>362.5230786672827</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>383.8034506311129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>408.2773388732868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -3815,7 +3815,7 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>466.3322427616885</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306">
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>476.1336616805589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>513.1259180316213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>534.6663684512442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>563.5636126501907</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>377.1028634437055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>415.5063964952727</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>428.161600698829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>346.4738225294045</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>114.8818779617646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -3936,7 +3936,7 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>24.89394584312811</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>59.82602132061476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>14.72291218578776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="381">
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>32.12862071037959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>75.28917408749045</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>78.1682369758712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384">
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>106.3654600698308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>198.0583384714527</v>
+        <v>0</v>
       </c>
     </row>
     <row r="386">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>0</v>
+        <v>61.84</v>
       </c>
     </row>
     <row r="387">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>0</v>
+        <v>360.94</v>
       </c>
     </row>
     <row r="388">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>0</v>
+        <v>186.08</v>
       </c>
     </row>
     <row r="389">
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>0</v>
+        <v>108.47</v>
       </c>
     </row>
     <row r="390">
@@ -4754,7 +4754,7 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>0</v>
+        <v>180.28</v>
       </c>
     </row>
     <row r="391">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>0</v>
+        <v>281.08</v>
       </c>
     </row>
     <row r="392">
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>0</v>
+        <v>91.39</v>
       </c>
     </row>
     <row r="393">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>0</v>
+        <v>130.01</v>
       </c>
     </row>
     <row r="394">
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>0</v>
+        <v>139.68</v>
       </c>
     </row>
     <row r="395">
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>0</v>
+        <v>287.22</v>
       </c>
     </row>
     <row r="397">
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>0</v>
+        <v>92.73999999999999</v>
       </c>
     </row>
     <row r="398">
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>0</v>
+        <v>206.55</v>
       </c>
     </row>
     <row r="399">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>0</v>
+        <v>201.97</v>
       </c>
     </row>
     <row r="400">
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="401">
@@ -4875,7 +4875,7 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>0</v>
+        <v>247.12</v>
       </c>
     </row>
     <row r="402">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>0</v>
+        <v>91.66</v>
       </c>
     </row>
     <row r="403">
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>0</v>
+        <v>388.95</v>
       </c>
     </row>
     <row r="404">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>0</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="405">
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>0</v>
+        <v>324.54</v>
       </c>
     </row>
     <row r="406">
@@ -4930,7 +4930,7 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>0</v>
+        <v>151.7</v>
       </c>
     </row>
     <row r="407">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>0</v>
+        <v>121.96</v>
       </c>
     </row>
     <row r="408">
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>0</v>
+        <v>463.2</v>
       </c>
     </row>
     <row r="409">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>0</v>
+        <v>276.29</v>
       </c>
     </row>
     <row r="410">
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>0</v>
+        <v>103.49</v>
       </c>
     </row>
     <row r="411">
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>0</v>
+        <v>192.79</v>
       </c>
     </row>
     <row r="414">
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>0</v>
+        <v>296.9</v>
       </c>
     </row>
     <row r="479">
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>0</v>
+        <v>298.83</v>
       </c>
     </row>
     <row r="480">
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>0</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="481">
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>0</v>
+        <v>74.23999999999999</v>
       </c>
     </row>
     <row r="483">
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>0</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="484">
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>0</v>
+        <v>236.24</v>
       </c>
     </row>
     <row r="485">
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>0</v>
+        <v>356.21</v>
       </c>
     </row>
     <row r="486">
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>0</v>
+        <v>95.43000000000001</v>
       </c>
     </row>
     <row r="487">
@@ -5821,7 +5821,7 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>0</v>
+        <v>92.97</v>
       </c>
     </row>
     <row r="488">
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>0</v>
+        <v>118.17</v>
       </c>
     </row>
     <row r="489">
@@ -5843,7 +5843,7 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>0</v>
+        <v>264.5</v>
       </c>
     </row>
     <row r="490">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>0</v>
+        <v>321.59</v>
       </c>
     </row>
     <row r="493">
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>0</v>
+        <v>92.33</v>
       </c>
     </row>
     <row r="494">
@@ -5898,7 +5898,7 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>0</v>
+        <v>276.02</v>
       </c>
     </row>
     <row r="495">
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>0</v>
+        <v>110.29</v>
       </c>
     </row>
     <row r="496">
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>0</v>
+        <v>24.63</v>
       </c>
     </row>
     <row r="497">
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>0</v>
+        <v>267.76</v>
       </c>
     </row>
     <row r="498">
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>0</v>
+        <v>107.86</v>
       </c>
     </row>
     <row r="499">
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>0</v>
+        <v>438.6899999999999</v>
       </c>
     </row>
     <row r="500">
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>0</v>
+        <v>126.56</v>
       </c>
     </row>
     <row r="501">
@@ -5975,7 +5975,7 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>0</v>
+        <v>479.7799999999999</v>
       </c>
     </row>
     <row r="502">
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>0</v>
+        <v>288.46</v>
       </c>
     </row>
     <row r="503">
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>0</v>
+        <v>209.48</v>
       </c>
     </row>
     <row r="504">
@@ -6008,7 +6008,7 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>0</v>
+        <v>428.5400000000001</v>
       </c>
     </row>
     <row r="505">
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>0</v>
+        <v>458.98</v>
       </c>
     </row>
     <row r="506">
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>0</v>
+        <v>223.1</v>
       </c>
     </row>
     <row r="507">
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>0</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="508">
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="C575" t="n">
-        <v>0</v>
+        <v>25.04</v>
       </c>
     </row>
     <row r="576">
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="C576" t="n">
-        <v>0</v>
+        <v>315.76</v>
       </c>
     </row>
     <row r="577">
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>0</v>
+        <v>183.57</v>
       </c>
     </row>
     <row r="578">
@@ -6826,7 +6826,7 @@
         </is>
       </c>
       <c r="C578" t="n">
-        <v>1065.019241300235</v>
+        <v>592.66</v>
       </c>
     </row>
     <row r="579">
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="C579" t="n">
-        <v>1076.267005813899</v>
+        <v>845.77</v>
       </c>
     </row>
     <row r="580">
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="C580" t="n">
-        <v>1073.951538426838</v>
+        <v>576.7</v>
       </c>
     </row>
     <row r="581">
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="C581" t="n">
-        <v>1071.636840170282</v>
+        <v>872.7500000000001</v>
       </c>
     </row>
     <row r="582">
@@ -6870,7 +6870,7 @@
         </is>
       </c>
       <c r="C582" t="n">
-        <v>1083.740262371408</v>
+        <v>592.55</v>
       </c>
     </row>
     <row r="583">
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="C583" t="n">
-        <v>1062.523028244362</v>
+        <v>817.1</v>
       </c>
     </row>
     <row r="584">
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="C584" t="n">
-        <v>1068.96872644641</v>
+        <v>605.34</v>
       </c>
     </row>
     <row r="585">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="C585" t="n">
-        <v>1072.738619619531</v>
+        <v>803.73</v>
       </c>
     </row>
     <row r="586">
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="C586" t="n">
-        <v>1059.165773587487</v>
+        <v>574.91</v>
       </c>
     </row>
     <row r="587">
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="C587" t="n">
-        <v>1070.404693100336</v>
+        <v>774.9400000000001</v>
       </c>
     </row>
     <row r="588">
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="C588" t="n">
-        <v>1055.813902844151</v>
+        <v>553.86</v>
       </c>
     </row>
     <row r="589">
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="C589" t="n">
-        <v>1056.717631188212</v>
+        <v>743.1900000000001</v>
       </c>
     </row>
     <row r="590">
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="C590" t="n">
-        <v>1048.959027213132</v>
+        <v>561.4400000000001</v>
       </c>
     </row>
     <row r="591">
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="C591" t="n">
-        <v>1053.189629559098</v>
+        <v>705.21</v>
       </c>
     </row>
     <row r="592">
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="C592" t="n">
-        <v>1041.203884325326</v>
+        <v>612.73</v>
       </c>
     </row>
     <row r="593">
@@ -6991,7 +6991,7 @@
         </is>
       </c>
       <c r="C593" t="n">
-        <v>1046.759698532413</v>
+        <v>638.13</v>
       </c>
     </row>
     <row r="594">
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="C594" t="n">
-        <v>1038.77073997091</v>
+        <v>639.16</v>
       </c>
     </row>
     <row r="595">
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="C595" t="n">
-        <v>1039.927127686056</v>
+        <v>625.05</v>
       </c>
     </row>
     <row r="596">
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="C596" t="n">
-        <v>1044.156576336264</v>
+        <v>572.37</v>
       </c>
     </row>
     <row r="597">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="C597" t="n">
-        <v>1028.845495361599</v>
+        <v>691.23</v>
       </c>
     </row>
     <row r="598">
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="C598" t="n">
-        <v>942.9763046309024</v>
+        <v>456.21</v>
       </c>
     </row>
     <row r="599">
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="C599" t="n">
-        <v>1008.941936138091</v>
+        <v>502.79</v>
       </c>
     </row>
     <row r="600">
@@ -7068,7 +7068,7 @@
         </is>
       </c>
       <c r="C600" t="n">
-        <v>938.2811474595638</v>
+        <v>627.47</v>
       </c>
     </row>
     <row r="601">
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="C601" t="n">
-        <v>917.1458257313625</v>
+        <v>376.38</v>
       </c>
     </row>
     <row r="602">
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="C602" t="n">
-        <v>748.3535986716103</v>
+        <v>486.7200000000001</v>
       </c>
     </row>
     <row r="603">
@@ -7101,7 +7101,7 @@
         </is>
       </c>
       <c r="C603" t="n">
-        <v>817.5922650453119</v>
+        <v>195.39</v>
       </c>
     </row>
     <row r="604">
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="C604" t="n">
-        <v>784.8680694242206</v>
+        <v>335.26</v>
       </c>
     </row>
     <row r="605">
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="C605" t="n">
-        <v>695.4720307601677</v>
+        <v>306.52</v>
       </c>
     </row>
     <row r="606">
@@ -7134,7 +7134,7 @@
         </is>
       </c>
       <c r="C606" t="n">
-        <v>348.5864814366337</v>
+        <v>99.15000000000001</v>
       </c>
     </row>
     <row r="607">
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="C609" t="n">
-        <v>267.9954488005091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="610">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="C610" t="n">
-        <v>222.4340804759645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="611">
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="C613" t="n">
-        <v>289.2622918451652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="614">
@@ -7244,7 +7244,7 @@
         </is>
       </c>
       <c r="C616" t="n">
-        <v>169.9105428148716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="617">
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="C618" t="n">
-        <v>343.1195018029412</v>
+        <v>0</v>
       </c>
     </row>
     <row r="619">
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="C619" t="n">
-        <v>545.0570234355921</v>
+        <v>0</v>
       </c>
     </row>
     <row r="620">
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="C620" t="n">
-        <v>517.905562892711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="621">
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="C621" t="n">
-        <v>366.6748926669632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="622">
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="C622" t="n">
-        <v>469.7191521526076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="623">
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="C623" t="n">
-        <v>600.1206145913767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="624">
@@ -7332,7 +7332,7 @@
         </is>
       </c>
       <c r="C624" t="n">
-        <v>499.4883483712445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="625">
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="C625" t="n">
-        <v>379.6093603793727</v>
+        <v>0</v>
       </c>
     </row>
     <row r="626">
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="C626" t="n">
-        <v>597.1809977990339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="627">
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="C627" t="n">
-        <v>658.0692142736079</v>
+        <v>0</v>
       </c>
     </row>
     <row r="628">
@@ -7376,7 +7376,7 @@
         </is>
       </c>
       <c r="C628" t="n">
-        <v>608.272244254811</v>
+        <v>0</v>
       </c>
     </row>
     <row r="629">
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="C629" t="n">
-        <v>634.2865453451858</v>
+        <v>0</v>
       </c>
     </row>
     <row r="630">
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="C630" t="n">
-        <v>700.1902618466743</v>
+        <v>0</v>
       </c>
     </row>
     <row r="631">
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="C631" t="n">
-        <v>595.6542737454494</v>
+        <v>0</v>
       </c>
     </row>
     <row r="632">
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="C632" t="n">
-        <v>661.9652448496446</v>
+        <v>0</v>
       </c>
     </row>
     <row r="633">
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="C633" t="n">
-        <v>630.1747736623324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="634">
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="C634" t="n">
-        <v>394.3120591241205</v>
+        <v>0</v>
       </c>
     </row>
     <row r="635">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="C635" t="n">
-        <v>305.535555082316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="636">
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="C636" t="n">
-        <v>471.248183597709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="637">
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="C637" t="n">
-        <v>430.9307470602375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="638">
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="C638" t="n">
-        <v>425.4295411190464</v>
+        <v>0</v>
       </c>
     </row>
     <row r="639">
@@ -7497,7 +7497,7 @@
         </is>
       </c>
       <c r="C639" t="n">
-        <v>523.4333038363447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="640">
@@ -7508,7 +7508,7 @@
         </is>
       </c>
       <c r="C640" t="n">
-        <v>503.0309634799652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="641">
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="C641" t="n">
-        <v>618.325933658555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="642">
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="C642" t="n">
-        <v>445.4603914412288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="643">
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="C643" t="n">
-        <v>252.6555254318849</v>
+        <v>0</v>
       </c>
     </row>
     <row r="644">
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="C644" t="n">
-        <v>266.7713776008719</v>
+        <v>0</v>
       </c>
     </row>
     <row r="645">
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="C645" t="n">
-        <v>269.6417726477121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="646">
@@ -7574,7 +7574,7 @@
         </is>
       </c>
       <c r="C646" t="n">
-        <v>560.3042665782934</v>
+        <v>0</v>
       </c>
     </row>
     <row r="647">
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="C647" t="n">
-        <v>594.2694542701449</v>
+        <v>0</v>
       </c>
     </row>
     <row r="648">
@@ -7596,7 +7596,7 @@
         </is>
       </c>
       <c r="C648" t="n">
-        <v>516.2269355642735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="649">
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="C649" t="n">
-        <v>627.3586023161359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="650">
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="C650" t="n">
-        <v>949.4135423973896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="651">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="C651" t="n">
-        <v>1277.751894144013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="652">
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="C652" t="n">
-        <v>1420.689414693299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="653">
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="C653" t="n">
-        <v>1289.739946769302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="654">
@@ -7662,7 +7662,7 @@
         </is>
       </c>
       <c r="C654" t="n">
-        <v>1142.615664312868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="655">
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="C655" t="n">
-        <v>1279.410139514053</v>
+        <v>0</v>
       </c>
     </row>
     <row r="656">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="C656" t="n">
-        <v>1238.098986363367</v>
+        <v>190.92</v>
       </c>
     </row>
     <row r="657">
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="C657" t="n">
-        <v>1125.21062553675</v>
+        <v>387.66</v>
       </c>
     </row>
     <row r="658">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="C658" t="n">
-        <v>1136.533764839961</v>
+        <v>371.3</v>
       </c>
     </row>
     <row r="659">
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="C659" t="n">
-        <v>1176.759290282015</v>
+        <v>128.51</v>
       </c>
     </row>
     <row r="660">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="C660" t="n">
-        <v>1100.346943682729</v>
+        <v>94.93000000000001</v>
       </c>
     </row>
     <row r="661">
@@ -7739,7 +7739,7 @@
         </is>
       </c>
       <c r="C661" t="n">
-        <v>1107.43755781371</v>
+        <v>149</v>
       </c>
     </row>
     <row r="662">
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="C662" t="n">
-        <v>1079.875381580847</v>
+        <v>182.61</v>
       </c>
     </row>
     <row r="663">
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="C663" t="n">
-        <v>1082.357365722367</v>
+        <v>238.94</v>
       </c>
     </row>
     <row r="664">
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="C664" t="n">
-        <v>1066.284460981921</v>
+        <v>460.88</v>
       </c>
     </row>
     <row r="665">
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="C665" t="n">
-        <v>1081.001388641022</v>
+        <v>246.32</v>
       </c>
     </row>
     <row r="666">
@@ -7794,7 +7794,7 @@
         </is>
       </c>
       <c r="C666" t="n">
-        <v>1140.269431705583</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="667">
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="C667" t="n">
-        <v>1124.039239776745</v>
+        <v>118.69</v>
       </c>
     </row>
     <row r="668">
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="C668" t="n">
-        <v>1185.617750880081</v>
+        <v>292.99</v>
       </c>
     </row>
     <row r="669">
@@ -7827,7 +7827,7 @@
         </is>
       </c>
       <c r="C669" t="n">
-        <v>1179.6358383729</v>
+        <v>124.59</v>
       </c>
     </row>
     <row r="670">
@@ -7838,7 +7838,7 @@
         </is>
       </c>
       <c r="C670" t="n">
-        <v>1254.015373045926</v>
+        <v>410.96</v>
       </c>
     </row>
     <row r="671">
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="C671" t="n">
-        <v>1249.215998691081</v>
+        <v>348.02</v>
       </c>
     </row>
     <row r="672">
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="C672" t="n">
-        <v>1240.81824726586</v>
+        <v>327.68</v>
       </c>
     </row>
     <row r="673">
@@ -7871,7 +7871,7 @@
         </is>
       </c>
       <c r="C673" t="n">
-        <v>1239.495727361508</v>
+        <v>700.72</v>
       </c>
     </row>
     <row r="674">
@@ -7882,7 +7882,7 @@
         </is>
       </c>
       <c r="C674" t="n">
-        <v>1234.552141036865</v>
+        <v>513.39</v>
       </c>
     </row>
     <row r="675">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="C675" t="n">
-        <v>1197.882305922127</v>
+        <v>885.03</v>
       </c>
     </row>
     <row r="676">
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="C676" t="n">
-        <v>1224.17733964704</v>
+        <v>660.59</v>
       </c>
     </row>
     <row r="677">
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="C677" t="n">
-        <v>1215.564231680255</v>
+        <v>955.1299999999999</v>
       </c>
     </row>
     <row r="678">
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="C678" t="n">
-        <v>1217.022887684095</v>
+        <v>707.5</v>
       </c>
     </row>
     <row r="679">
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="C679" t="n">
-        <v>1168.634580186276</v>
+        <v>925.29</v>
       </c>
     </row>
     <row r="680">
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="C680" t="n">
-        <v>1194.710027151845</v>
+        <v>763.6</v>
       </c>
     </row>
     <row r="681">
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="C681" t="n">
-        <v>1158.18671139842</v>
+        <v>853.4399999999999</v>
       </c>
     </row>
     <row r="682">
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="C682" t="n">
-        <v>1189.152290118493</v>
+        <v>780.08</v>
       </c>
     </row>
     <row r="683">
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="C683" t="n">
-        <v>1147.309283223195</v>
+        <v>702.1799999999999</v>
       </c>
     </row>
     <row r="684">
@@ -7992,7 +7992,7 @@
         </is>
       </c>
       <c r="C684" t="n">
-        <v>1181.109492421599</v>
+        <v>857.27</v>
       </c>
     </row>
     <row r="685">
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="C685" t="n">
-        <v>1141.345445282896</v>
+        <v>723.98</v>
       </c>
     </row>
     <row r="686">
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="C686" t="n">
-        <v>1178.10834518881</v>
+        <v>727.6799999999999</v>
       </c>
     </row>
     <row r="687">
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="C687" t="n">
-        <v>1151.523733828544</v>
+        <v>862.3099999999999</v>
       </c>
     </row>
     <row r="688">
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c r="C688" t="n">
-        <v>1162.449617225621</v>
+        <v>705.4</v>
       </c>
     </row>
     <row r="689">
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="C689" t="n">
-        <v>1159.221191928431</v>
+        <v>806.4299999999999</v>
       </c>
     </row>
     <row r="690">
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="C690" t="n">
-        <v>1160.731764241398</v>
+        <v>855.97</v>
       </c>
     </row>
     <row r="691">
@@ -8069,7 +8069,7 @@
         </is>
       </c>
       <c r="C691" t="n">
-        <v>1137.841286699454</v>
+        <v>732.34</v>
       </c>
     </row>
     <row r="692">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="C692" t="n">
-        <v>1120.002842883439</v>
+        <v>924.8200000000002</v>
       </c>
     </row>
     <row r="693">
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="C693" t="n">
-        <v>1156.47731884976</v>
+        <v>854.7799999999999</v>
       </c>
     </row>
     <row r="694">
@@ -8102,7 +8102,7 @@
         </is>
       </c>
       <c r="C694" t="n">
-        <v>998.6167436658754</v>
+        <v>691.5700000000001</v>
       </c>
     </row>
     <row r="695">
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="C695" t="n">
-        <v>1057.852483249202</v>
+        <v>835.4599999999999</v>
       </c>
     </row>
     <row r="696">
@@ -8124,7 +8124,7 @@
         </is>
       </c>
       <c r="C696" t="n">
-        <v>1023.883065339569</v>
+        <v>612.54</v>
       </c>
     </row>
     <row r="697">
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="C697" t="n">
-        <v>977.331441489085</v>
+        <v>792.46</v>
       </c>
     </row>
     <row r="698">
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="C698" t="n">
-        <v>867.875325543638</v>
+        <v>497.77</v>
       </c>
     </row>
     <row r="699">
@@ -8157,7 +8157,7 @@
         </is>
       </c>
       <c r="C699" t="n">
-        <v>882.4076618813989</v>
+        <v>488.92</v>
       </c>
     </row>
     <row r="700">
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="C700" t="n">
-        <v>808.9153192465637</v>
+        <v>682.65</v>
       </c>
     </row>
     <row r="701">
@@ -8179,7 +8179,7 @@
         </is>
       </c>
       <c r="C701" t="n">
-        <v>782.7375779237523</v>
+        <v>277.92</v>
       </c>
     </row>
     <row r="702">
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="C702" t="n">
-        <v>484.2745624055359</v>
+        <v>118.26</v>
       </c>
     </row>
     <row r="703">
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="C703" t="n">
-        <v>94.28001737451238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="704">
@@ -8212,7 +8212,7 @@
         </is>
       </c>
       <c r="C704" t="n">
-        <v>70.78538782043154</v>
+        <v>0</v>
       </c>
     </row>
     <row r="705">
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="C705" t="n">
-        <v>284.1875687693207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="706">
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="C706" t="n">
-        <v>287.0975740371985</v>
+        <v>0</v>
       </c>
     </row>
     <row r="707">
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="C709" t="n">
-        <v>201.1218587314789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="710">
@@ -8322,7 +8322,7 @@
         </is>
       </c>
       <c r="C714" t="n">
-        <v>112.5753247108439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="715">
@@ -8333,7 +8333,7 @@
         </is>
       </c>
       <c r="C715" t="n">
-        <v>213.1860552768199</v>
+        <v>0</v>
       </c>
     </row>
     <row r="716">
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="C716" t="n">
-        <v>90.71202095910724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="717">
@@ -8355,7 +8355,7 @@
         </is>
       </c>
       <c r="C717" t="n">
-        <v>7.347888285098744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="718">
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="C718" t="n">
-        <v>67.39352229080517</v>
+        <v>0</v>
       </c>
     </row>
     <row r="719">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="C719" t="n">
-        <v>94.79264285648426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="720">
@@ -8388,7 +8388,7 @@
         </is>
       </c>
       <c r="C720" t="n">
-        <v>36.80443295321558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="721">
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="C727" t="n">
-        <v>5.408910280520951</v>
+        <v>0</v>
       </c>
     </row>
     <row r="728">
@@ -8476,7 +8476,7 @@
         </is>
       </c>
       <c r="C728" t="n">
-        <v>72.48785819454218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="729">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="C736" t="n">
-        <v>44.07463905725032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="737">
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="C741" t="n">
-        <v>123.2639313469477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="742">
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="C742" t="n">
-        <v>204.447579037625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="743">
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="C743" t="n">
-        <v>237.2090774882371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="744">
@@ -8652,7 +8652,7 @@
         </is>
       </c>
       <c r="C744" t="n">
-        <v>202.6455062630412</v>
+        <v>0</v>
       </c>
     </row>
     <row r="745">
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="C745" t="n">
-        <v>234.28676613227</v>
+        <v>0</v>
       </c>
     </row>
     <row r="746">
@@ -8674,7 +8674,7 @@
         </is>
       </c>
       <c r="C746" t="n">
-        <v>554.8722823826049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="747">
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="C747" t="n">
-        <v>763.2566559130629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="748">
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="C748" t="n">
-        <v>857.0601969393656</v>
+        <v>0</v>
       </c>
     </row>
     <row r="749">
@@ -8707,7 +8707,7 @@
         </is>
       </c>
       <c r="C749" t="n">
-        <v>803.8625163901282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="750">
@@ -8718,7 +8718,7 @@
         </is>
       </c>
       <c r="C750" t="n">
-        <v>776.2564997184469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="751">
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="C751" t="n">
-        <v>869.5258796086217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="752">
@@ -8740,7 +8740,7 @@
         </is>
       </c>
       <c r="C752" t="n">
-        <v>855.5265507112306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="753">
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="C753" t="n">
-        <v>828.200882108835</v>
+        <v>0</v>
       </c>
     </row>
     <row r="754">
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="C754" t="n">
-        <v>878.9511893893033</v>
+        <v>256.89</v>
       </c>
     </row>
     <row r="755">
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="C755" t="n">
-        <v>913.5393727906782</v>
+        <v>360.24</v>
       </c>
     </row>
     <row r="756">
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="C756" t="n">
-        <v>897.0588288822725</v>
+        <v>313.91</v>
       </c>
     </row>
     <row r="757">
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="C757" t="n">
-        <v>901.2302081793082</v>
+        <v>0</v>
       </c>
     </row>
     <row r="758">
@@ -8806,7 +8806,7 @@
         </is>
       </c>
       <c r="C758" t="n">
-        <v>888.0611556626957</v>
+        <v>86.04000000000001</v>
       </c>
     </row>
     <row r="759">
@@ -8817,7 +8817,7 @@
         </is>
       </c>
       <c r="C759" t="n">
-        <v>902.4119772011384</v>
+        <v>114.81</v>
       </c>
     </row>
     <row r="760">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="C760" t="n">
-        <v>928.7881541943907</v>
+        <v>133.27</v>
       </c>
     </row>
     <row r="761">
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="C761" t="n">
-        <v>905.1996907186285</v>
+        <v>268.98</v>
       </c>
     </row>
     <row r="762">
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="C762" t="n">
-        <v>984.1663197269592</v>
+        <v>464.5799999999999</v>
       </c>
     </row>
     <row r="763">
@@ -8861,7 +8861,7 @@
         </is>
       </c>
       <c r="C763" t="n">
-        <v>965.8083282544226</v>
+        <v>162.18</v>
       </c>
     </row>
     <row r="764">
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="C764" t="n">
-        <v>986.8005917085852</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="765">
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="C765" t="n">
-        <v>1004.863237066977</v>
+        <v>103.08</v>
       </c>
     </row>
     <row r="766">
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="C766" t="n">
-        <v>1054.432929021374</v>
+        <v>420.54</v>
       </c>
     </row>
     <row r="767">
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="C767" t="n">
-        <v>1063.980915117697</v>
+        <v>263.54</v>
       </c>
     </row>
     <row r="768">
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="C768" t="n">
-        <v>1078.545170371439</v>
+        <v>238.87</v>
       </c>
     </row>
     <row r="769">
@@ -8927,7 +8927,7 @@
         </is>
       </c>
       <c r="C769" t="n">
-        <v>1088.729611961132</v>
+        <v>532.83</v>
       </c>
     </row>
     <row r="770">
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="C770" t="n">
-        <v>1319.303615934236</v>
+        <v>1336.73</v>
       </c>
     </row>
     <row r="771">
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="C771" t="n">
-        <v>1329.565478200622</v>
+        <v>1321.34</v>
       </c>
     </row>
     <row r="772">
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="C772" t="n">
-        <v>1316.430790434998</v>
+        <v>1274.14</v>
       </c>
     </row>
     <row r="773">
@@ -8975,7 +8975,7 @@
         </is>
       </c>
       <c r="C773" t="n">
-        <v>1332.73026563978</v>
+        <v>1252.82</v>
       </c>
     </row>
     <row r="774">
@@ -8986,7 +8986,7 @@
         </is>
       </c>
       <c r="C774" t="n">
-        <v>1362.911531218088</v>
+        <v>1282.38</v>
       </c>
     </row>
     <row r="775">
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="C775" t="n">
-        <v>1322.110450036095</v>
+        <v>1306.01</v>
       </c>
     </row>
     <row r="776">
@@ -9008,7 +9008,7 @@
         </is>
       </c>
       <c r="C776" t="n">
-        <v>1358.822064319897</v>
+        <v>1287.64</v>
       </c>
     </row>
     <row r="777">
@@ -9019,7 +9019,7 @@
         </is>
       </c>
       <c r="C777" t="n">
-        <v>1366.767028616481</v>
+        <v>1280.05</v>
       </c>
     </row>
     <row r="778">
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="C778" t="n">
-        <v>1382.182619044244</v>
+        <v>1264.69</v>
       </c>
     </row>
     <row r="779">
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="C779" t="n">
-        <v>1388.67617254635</v>
+        <v>1284.08</v>
       </c>
     </row>
     <row r="780">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="C780" t="n">
-        <v>1424.193942459384</v>
+        <v>1355.58</v>
       </c>
     </row>
     <row r="781">
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="C781" t="n">
-        <v>1385.484188652515</v>
+        <v>1357.85</v>
       </c>
     </row>
     <row r="782">
@@ -9074,7 +9074,7 @@
         </is>
       </c>
       <c r="C782" t="n">
-        <v>1417.330837131955</v>
+        <v>1326.72</v>
       </c>
     </row>
     <row r="783">
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="C783" t="n">
-        <v>1409.357876484968</v>
+        <v>1293.12</v>
       </c>
     </row>
     <row r="784">
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="C784" t="n">
-        <v>1378.50869797561</v>
+        <v>1278.2</v>
       </c>
     </row>
     <row r="785">
@@ -9107,7 +9107,7 @@
         </is>
       </c>
       <c r="C785" t="n">
-        <v>1441.028947852593</v>
+        <v>1340.9</v>
       </c>
     </row>
     <row r="786">
@@ -9118,7 +9118,7 @@
         </is>
       </c>
       <c r="C786" t="n">
-        <v>1435.885218387788</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="787">
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="C787" t="n">
-        <v>1405.7867420171</v>
+        <v>1312.72</v>
       </c>
     </row>
     <row r="788">
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="C788" t="n">
-        <v>1374.946762308589</v>
+        <v>1277.27</v>
       </c>
     </row>
     <row r="789">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="C789" t="n">
-        <v>1413.272166219207</v>
+        <v>1280.6</v>
       </c>
     </row>
     <row r="790">
@@ -9162,7 +9162,7 @@
         </is>
       </c>
       <c r="C790" t="n">
-        <v>1298.223963872029</v>
+        <v>1300.89</v>
       </c>
     </row>
     <row r="791">
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="C791" t="n">
-        <v>1301.264767473687</v>
+        <v>1269.17</v>
       </c>
     </row>
     <row r="792">
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="C792" t="n">
-        <v>1286.959832261207</v>
+        <v>1257.11</v>
       </c>
     </row>
     <row r="793">
@@ -9195,7 +9195,7 @@
         </is>
       </c>
       <c r="C793" t="n">
-        <v>1270.07283364582</v>
+        <v>1246.29</v>
       </c>
     </row>
     <row r="794">
@@ -9206,7 +9206,7 @@
         </is>
       </c>
       <c r="C794" t="n">
-        <v>1190.208844694014</v>
+        <v>1176.71</v>
       </c>
     </row>
     <row r="795">
@@ -9217,7 +9217,7 @@
         </is>
       </c>
       <c r="C795" t="n">
-        <v>1127.794181052838</v>
+        <v>1140.6</v>
       </c>
     </row>
     <row r="796">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="C796" t="n">
-        <v>1110.021697868982</v>
+        <v>1120.77</v>
       </c>
     </row>
     <row r="797">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="C797" t="n">
-        <v>1122.50287082662</v>
+        <v>1172.53</v>
       </c>
     </row>
     <row r="798">
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="C798" t="n">
-        <v>923.6571922959778</v>
+        <v>1033.45</v>
       </c>
     </row>
     <row r="799">
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="C799" t="n">
-        <v>672.4043455497369</v>
+        <v>593.79</v>
       </c>
     </row>
     <row r="800">
@@ -9272,7 +9272,7 @@
         </is>
       </c>
       <c r="C800" t="n">
-        <v>660.6562770248009</v>
+        <v>594.75</v>
       </c>
     </row>
     <row r="801">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="C801" t="n">
-        <v>719.3650237683112</v>
+        <v>599.02</v>
       </c>
     </row>
     <row r="802">
@@ -9294,7 +9294,7 @@
         </is>
       </c>
       <c r="C802" t="n">
-        <v>711.4424565520499</v>
+        <v>542.34</v>
       </c>
     </row>
     <row r="803">
@@ -9305,7 +9305,7 @@
         </is>
       </c>
       <c r="C803" t="n">
-        <v>583.1391821325146</v>
+        <v>305.56</v>
       </c>
     </row>
     <row r="804">
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="C804" t="n">
-        <v>506.1736153431723</v>
+        <v>485.79</v>
       </c>
     </row>
     <row r="805">
@@ -9327,7 +9327,7 @@
         </is>
       </c>
       <c r="C805" t="n">
-        <v>611.8502393667886</v>
+        <v>290.87</v>
       </c>
     </row>
     <row r="806">
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="C806" t="n">
-        <v>442.5683069141311</v>
+        <v>148.01</v>
       </c>
     </row>
     <row r="807">
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="C807" t="n">
-        <v>185.1774603159058</v>
+        <v>0</v>
       </c>
     </row>
     <row r="808">
@@ -9360,7 +9360,7 @@
         </is>
       </c>
       <c r="C808" t="n">
-        <v>93.47301488283318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="809">
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="C809" t="n">
-        <v>69.50413945900915</v>
+        <v>0</v>
       </c>
     </row>
     <row r="810">
@@ -9382,7 +9382,7 @@
         </is>
       </c>
       <c r="C810" t="n">
-        <v>125.6208241030397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="811">
@@ -9393,7 +9393,7 @@
         </is>
       </c>
       <c r="C811" t="n">
-        <v>126.9114558566303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="812">
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="C812" t="n">
-        <v>140.5896727679398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="813">
@@ -9415,7 +9415,7 @@
         </is>
       </c>
       <c r="C813" t="n">
-        <v>83.07757003023792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="814">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="C824" t="n">
-        <v>27.88556484524087</v>
+        <v>0</v>
       </c>
     </row>
     <row r="825">
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="C825" t="n">
-        <v>6.059610070855304</v>
+        <v>0</v>
       </c>
     </row>
     <row r="826">
@@ -9624,7 +9624,7 @@
         </is>
       </c>
       <c r="C832" t="n">
-        <v>49.73711628285228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="833">
@@ -9635,7 +9635,7 @@
         </is>
       </c>
       <c r="C833" t="n">
-        <v>142.019086429958</v>
+        <v>0</v>
       </c>
     </row>
     <row r="834">
@@ -9646,7 +9646,7 @@
         </is>
       </c>
       <c r="C834" t="n">
-        <v>93.19705085742959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="835">
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="C835" t="n">
-        <v>128.2216850555031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="836">
@@ -9668,7 +9668,7 @@
         </is>
       </c>
       <c r="C836" t="n">
-        <v>258.8130611987111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="837">
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="C837" t="n">
-        <v>438.8023978370291</v>
+        <v>201.88</v>
       </c>
     </row>
     <row r="838">
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="C838" t="n">
-        <v>589.6315357910318</v>
+        <v>616.91</v>
       </c>
     </row>
     <row r="839">
@@ -9701,7 +9701,7 @@
         </is>
       </c>
       <c r="C839" t="n">
-        <v>628.6672471061672</v>
+        <v>498.4499999999999</v>
       </c>
     </row>
     <row r="840">
@@ -9712,7 +9712,7 @@
         </is>
       </c>
       <c r="C840" t="n">
-        <v>652.8252978691448</v>
+        <v>276.35</v>
       </c>
     </row>
     <row r="841">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="C841" t="n">
-        <v>656.7131910444325</v>
+        <v>137.68</v>
       </c>
     </row>
     <row r="842">
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="C842" t="n">
-        <v>863.458239815288</v>
+        <v>426.99</v>
       </c>
     </row>
     <row r="843">
@@ -9745,7 +9745,7 @@
         </is>
       </c>
       <c r="C843" t="n">
-        <v>1045.490110189455</v>
+        <v>957.45</v>
       </c>
     </row>
     <row r="844">
@@ -9756,7 +9756,7 @@
         </is>
       </c>
       <c r="C844" t="n">
-        <v>1077.40075032696</v>
+        <v>1156.3</v>
       </c>
     </row>
     <row r="845">
@@ -9767,7 +9767,7 @@
         </is>
       </c>
       <c r="C845" t="n">
-        <v>1030.227699793184</v>
+        <v>1058.59</v>
       </c>
     </row>
     <row r="846">
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="C846" t="n">
-        <v>958.8814004776403</v>
+        <v>852.0900000000001</v>
       </c>
     </row>
     <row r="847">
@@ -9789,7 +9789,7 @@
         </is>
       </c>
       <c r="C847" t="n">
-        <v>985.6135156862665</v>
+        <v>686.9299999999999</v>
       </c>
     </row>
     <row r="848">
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="C848" t="n">
-        <v>1012.218047526627</v>
+        <v>880.9800000000001</v>
       </c>
     </row>
     <row r="849">
@@ -9811,7 +9811,7 @@
         </is>
       </c>
       <c r="C849" t="n">
-        <v>1026.242619287211</v>
+        <v>837.3299999999999</v>
       </c>
     </row>
     <row r="850">
@@ -9822,7 +9822,7 @@
         </is>
       </c>
       <c r="C850" t="n">
-        <v>1051.857280166884</v>
+        <v>841.48</v>
       </c>
     </row>
     <row r="851">
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="C851" t="n">
-        <v>1085.528890744754</v>
+        <v>908.2900000000001</v>
       </c>
     </row>
     <row r="852">
@@ -9844,7 +9844,7 @@
         </is>
       </c>
       <c r="C852" t="n">
-        <v>1126.463154565094</v>
+        <v>834.3500000000001</v>
       </c>
     </row>
     <row r="853">
@@ -9855,7 +9855,7 @@
         </is>
       </c>
       <c r="C853" t="n">
-        <v>1152.855714038115</v>
+        <v>1003.41</v>
       </c>
     </row>
     <row r="854">
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="C854" t="n">
-        <v>1155.360587503481</v>
+        <v>1015.84</v>
       </c>
     </row>
     <row r="855">
@@ -9877,7 +9877,7 @@
         </is>
       </c>
       <c r="C855" t="n">
-        <v>1164.704169476639</v>
+        <v>970.86</v>
       </c>
     </row>
     <row r="856">
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="C856" t="n">
-        <v>1175.311986644437</v>
+        <v>959.61</v>
       </c>
     </row>
     <row r="857">
@@ -9899,7 +9899,7 @@
         </is>
       </c>
       <c r="C857" t="n">
-        <v>1171.238917608625</v>
+        <v>1044.77</v>
       </c>
     </row>
     <row r="858">
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="C858" t="n">
-        <v>1202.82320029</v>
+        <v>1034.25</v>
       </c>
     </row>
     <row r="859">
@@ -9921,7 +9921,7 @@
         </is>
       </c>
       <c r="C859" t="n">
-        <v>1233.23603568093</v>
+        <v>1055.11</v>
       </c>
     </row>
     <row r="860">
@@ -9932,7 +9932,7 @@
         </is>
       </c>
       <c r="C860" t="n">
-        <v>1231.867814041936</v>
+        <v>1074.48</v>
       </c>
     </row>
     <row r="861">
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="C861" t="n">
-        <v>1252.500724341279</v>
+        <v>1071.25</v>
       </c>
     </row>
     <row r="862">
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="C862" t="n">
-        <v>1294.625233001621</v>
+        <v>1133.2</v>
       </c>
     </row>
     <row r="863">
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="C863" t="n">
-        <v>1313.117622338703</v>
+        <v>1160.92</v>
       </c>
     </row>
     <row r="864">
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="C864" t="n">
-        <v>1351.668596843999</v>
+        <v>1191.3</v>
       </c>
     </row>
     <row r="865">
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="C865" t="n">
-        <v>1339.811742500354</v>
+        <v>1226.28</v>
       </c>
     </row>
     <row r="866">
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="C866" t="n">
-        <v>1326.302703535052</v>
+        <v>1247.63</v>
       </c>
     </row>
     <row r="867">
@@ -10009,7 +10009,7 @@
         </is>
       </c>
       <c r="C867" t="n">
-        <v>1344.201570243586</v>
+        <v>1249.88</v>
       </c>
     </row>
     <row r="868">
@@ -10020,7 +10020,7 @@
         </is>
       </c>
       <c r="C868" t="n">
-        <v>1370.840897548018</v>
+        <v>1241.91</v>
       </c>
     </row>
     <row r="869">
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="C869" t="n">
-        <v>1392.627257483977</v>
+        <v>1221.12</v>
       </c>
     </row>
     <row r="870">
@@ -10042,7 +10042,7 @@
         </is>
       </c>
       <c r="C870" t="n">
-        <v>1452.533048181158</v>
+        <v>1238.6</v>
       </c>
     </row>
     <row r="871">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="C871" t="n">
-        <v>1471.562967445983</v>
+        <v>1260.6</v>
       </c>
     </row>
     <row r="872">
@@ -10064,7 +10064,7 @@
         </is>
       </c>
       <c r="C872" t="n">
-        <v>1522.780690717305</v>
+        <v>1277.06</v>
       </c>
     </row>
     <row r="873">
@@ -10075,7 +10075,7 @@
         </is>
       </c>
       <c r="C873" t="n">
-        <v>1402.320793837176</v>
+        <v>1267.04</v>
       </c>
     </row>
     <row r="874">
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="C874" t="n">
-        <v>1446.615819549496</v>
+        <v>1260.65</v>
       </c>
     </row>
     <row r="875">
@@ -10097,7 +10097,7 @@
         </is>
       </c>
       <c r="C875" t="n">
-        <v>1459.257771548022</v>
+        <v>1242.17</v>
       </c>
     </row>
     <row r="876">
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="C876" t="n">
-        <v>1479.996268083172</v>
+        <v>1288.26</v>
       </c>
     </row>
     <row r="877">
@@ -10119,7 +10119,7 @@
         </is>
       </c>
       <c r="C877" t="n">
-        <v>1486.365037852052</v>
+        <v>1312.85</v>
       </c>
     </row>
     <row r="878">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="C878" t="n">
-        <v>1664.22</v>
+        <v>1300.31</v>
       </c>
     </row>
     <row r="879">
@@ -10141,7 +10141,7 @@
         </is>
       </c>
       <c r="C879" t="n">
-        <v>1540.858334120556</v>
+        <v>1266.69</v>
       </c>
     </row>
     <row r="880">
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="C880" t="n">
-        <v>1399.068817763905</v>
+        <v>1249.67</v>
       </c>
     </row>
     <row r="881">
@@ -10163,7 +10163,7 @@
         </is>
       </c>
       <c r="C881" t="n">
-        <v>1429.995986106529</v>
+        <v>1272.1</v>
       </c>
     </row>
     <row r="882">
@@ -10174,7 +10174,7 @@
         </is>
       </c>
       <c r="C882" t="n">
-        <v>1395.957623338377</v>
+        <v>1315.97</v>
       </c>
     </row>
     <row r="883">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="C883" t="n">
-        <v>1464.893436884199</v>
+        <v>1322.83</v>
       </c>
     </row>
     <row r="884">
@@ -10196,7 +10196,7 @@
         </is>
       </c>
       <c r="C884" t="n">
-        <v>1497.009250275373</v>
+        <v>1284.89</v>
       </c>
     </row>
     <row r="885">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="C885" t="n">
-        <v>1506.763178755871</v>
+        <v>1243.76</v>
       </c>
     </row>
     <row r="886">
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="C886" t="n">
-        <v>1309.728464148457</v>
+        <v>1205.27</v>
       </c>
     </row>
     <row r="887">
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="C887" t="n">
-        <v>1281.739712754587</v>
+        <v>1206.18</v>
       </c>
     </row>
     <row r="888">
@@ -10240,7 +10240,7 @@
         </is>
       </c>
       <c r="C888" t="n">
-        <v>1284.440160724913</v>
+        <v>1207.99</v>
       </c>
     </row>
     <row r="889">
@@ -10251,7 +10251,7 @@
         </is>
       </c>
       <c r="C889" t="n">
-        <v>1275.933269680949</v>
+        <v>1202.29</v>
       </c>
     </row>
     <row r="890">
@@ -10262,7 +10262,7 @@
         </is>
       </c>
       <c r="C890" t="n">
-        <v>1204.50218141847</v>
+        <v>1118.17</v>
       </c>
     </row>
     <row r="891">
@@ -10273,7 +10273,7 @@
         </is>
       </c>
       <c r="C891" t="n">
-        <v>1111.312329622573</v>
+        <v>1044.37</v>
       </c>
     </row>
     <row r="892">
@@ -10284,7 +10284,7 @@
         </is>
       </c>
       <c r="C892" t="n">
-        <v>1117.190363363669</v>
+        <v>1014.28</v>
       </c>
     </row>
     <row r="893">
@@ -10295,7 +10295,7 @@
         </is>
       </c>
       <c r="C893" t="n">
-        <v>1093.854205458959</v>
+        <v>1006.87</v>
       </c>
     </row>
     <row r="894">
@@ -10306,7 +10306,7 @@
         </is>
       </c>
       <c r="C894" t="n">
-        <v>921.8738247752898</v>
+        <v>673.2</v>
       </c>
     </row>
     <row r="895">
@@ -10317,7 +10317,7 @@
         </is>
       </c>
       <c r="C895" t="n">
-        <v>703.8822420995796</v>
+        <v>380.11</v>
       </c>
     </row>
     <row r="896">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="C896" t="n">
-        <v>685.6754155366103</v>
+        <v>415.5</v>
       </c>
     </row>
     <row r="897">
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="C897" t="n">
-        <v>774.5122347926629</v>
+        <v>483.39</v>
       </c>
     </row>
     <row r="898">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="C898" t="n">
-        <v>734.3486705041386</v>
+        <v>462.99</v>
       </c>
     </row>
     <row r="899">
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="C899" t="n">
-        <v>571.2679296658041</v>
+        <v>300.74</v>
       </c>
     </row>
     <row r="900">
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="C900" t="n">
-        <v>455.609006931972</v>
+        <v>133.77</v>
       </c>
     </row>
     <row r="901">
@@ -10383,7 +10383,7 @@
         </is>
       </c>
       <c r="C901" t="n">
-        <v>548.9636372473857</v>
+        <v>133.36</v>
       </c>
     </row>
     <row r="902">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="C902" t="n">
-        <v>356.7538936580426</v>
+        <v>192.72</v>
       </c>
     </row>
     <row r="903">
@@ -10405,7 +10405,7 @@
         </is>
       </c>
       <c r="C903" t="n">
-        <v>88.30608844197916</v>
+        <v>96.29000000000001</v>
       </c>
     </row>
     <row r="904">
@@ -10416,7 +10416,7 @@
         </is>
       </c>
       <c r="C904" t="n">
-        <v>96.80338073723307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="905">
@@ -10438,7 +10438,7 @@
         </is>
       </c>
       <c r="C906" t="n">
-        <v>219.0786409670826</v>
+        <v>0</v>
       </c>
     </row>
     <row r="907">
@@ -10449,7 +10449,7 @@
         </is>
       </c>
       <c r="C907" t="n">
-        <v>344.2663215345976</v>
+        <v>0</v>
       </c>
     </row>
     <row r="908">
@@ -10460,7 +10460,7 @@
         </is>
       </c>
       <c r="C908" t="n">
-        <v>308.7897462514428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="909">
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="C909" t="n">
-        <v>236.1556148173486</v>
+        <v>0</v>
       </c>
     </row>
     <row r="910">
@@ -10482,7 +10482,7 @@
         </is>
       </c>
       <c r="C910" t="n">
-        <v>340.2008515081804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="911">
@@ -10493,7 +10493,7 @@
         </is>
       </c>
       <c r="C911" t="n">
-        <v>456.8792413445545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="912">
@@ -10504,7 +10504,7 @@
         </is>
       </c>
       <c r="C912" t="n">
-        <v>453.048940661525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="913">
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="C913" t="n">
-        <v>411.1767991026755</v>
+        <v>0</v>
       </c>
     </row>
     <row r="914">
@@ -10526,7 +10526,7 @@
         </is>
       </c>
       <c r="C914" t="n">
-        <v>463.5607703422252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="915">
@@ -10537,7 +10537,7 @@
         </is>
       </c>
       <c r="C915" t="n">
-        <v>472.7967663402624</v>
+        <v>0</v>
       </c>
     </row>
     <row r="916">
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="C916" t="n">
-        <v>403.9301437747218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="917">
@@ -10559,7 +10559,7 @@
         </is>
       </c>
       <c r="C917" t="n">
-        <v>454.4371596936639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="918">
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="C918" t="n">
-        <v>424.2314972957183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="919">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="C919" t="n">
-        <v>335.3798799687383</v>
+        <v>0</v>
       </c>
     </row>
     <row r="920">
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="C920" t="n">
-        <v>369.1090830388665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="921">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="C921" t="n">
-        <v>339.2393768457598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="922">
@@ -10614,7 +10614,7 @@
         </is>
       </c>
       <c r="C922" t="n">
-        <v>278.5244916219243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="923">
@@ -10625,7 +10625,7 @@
         </is>
       </c>
       <c r="C923" t="n">
-        <v>218.0451756893392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="924">
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="C924" t="n">
-        <v>282.9427156634225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="925">
@@ -10647,7 +10647,7 @@
         </is>
       </c>
       <c r="C925" t="n">
-        <v>265.0986418121071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="926">
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="C926" t="n">
-        <v>360.2050437670394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="927">
@@ -10669,7 +10669,7 @@
         </is>
       </c>
       <c r="C927" t="n">
-        <v>462.6496891105303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="928">
@@ -10680,7 +10680,7 @@
         </is>
       </c>
       <c r="C928" t="n">
-        <v>495.819765068319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="929">
@@ -10691,7 +10691,7 @@
         </is>
       </c>
       <c r="C929" t="n">
-        <v>543.4383575213699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="930">
@@ -10702,7 +10702,7 @@
         </is>
       </c>
       <c r="C930" t="n">
-        <v>365.3583719805547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="931">
@@ -10713,7 +10713,7 @@
         </is>
       </c>
       <c r="C931" t="n">
-        <v>295.6046650550936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="932">
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="C932" t="n">
-        <v>349.4548451600484</v>
+        <v>0</v>
       </c>
     </row>
     <row r="933">
@@ -10735,7 +10735,7 @@
         </is>
       </c>
       <c r="C933" t="n">
-        <v>391.7757282210757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="934">
@@ -10746,7 +10746,7 @@
         </is>
       </c>
       <c r="C934" t="n">
-        <v>485.6818866394337</v>
+        <v>153.45</v>
       </c>
     </row>
     <row r="935">
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="C935" t="n">
-        <v>598.6119651046733</v>
+        <v>600.12</v>
       </c>
     </row>
     <row r="936">
@@ -10768,7 +10768,7 @@
         </is>
       </c>
       <c r="C936" t="n">
-        <v>643.7984746034065</v>
+        <v>500.7799999999999</v>
       </c>
     </row>
     <row r="937">
@@ -10779,7 +10779,7 @@
         </is>
       </c>
       <c r="C937" t="n">
-        <v>702.0664788019964</v>
+        <v>309.42</v>
       </c>
     </row>
     <row r="938">
@@ -10790,7 +10790,7 @@
         </is>
       </c>
       <c r="C938" t="n">
-        <v>944.5864639617329</v>
+        <v>345.12</v>
       </c>
     </row>
     <row r="939">
@@ -10801,7 +10801,7 @@
         </is>
       </c>
       <c r="C939" t="n">
-        <v>1221.734335039542</v>
+        <v>829.1900000000001</v>
       </c>
     </row>
     <row r="940">
@@ -10812,7 +10812,7 @@
         </is>
       </c>
       <c r="C940" t="n">
-        <v>1306.785247825348</v>
+        <v>942.53</v>
       </c>
     </row>
     <row r="941">
@@ -10823,7 +10823,7 @@
         </is>
       </c>
       <c r="C941" t="n">
-        <v>1245.530033038729</v>
+        <v>748.13</v>
       </c>
     </row>
     <row r="942">
@@ -10834,7 +10834,7 @@
         </is>
       </c>
       <c r="C942" t="n">
-        <v>1150.286448966821</v>
+        <v>927.4199999999998</v>
       </c>
     </row>
     <row r="943">
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="C943" t="n">
-        <v>1187.234432437599</v>
+        <v>817.33</v>
       </c>
     </row>
     <row r="944">
@@ -10856,7 +10856,7 @@
         </is>
       </c>
       <c r="C944" t="n">
-        <v>1134.546900770105</v>
+        <v>824.91</v>
       </c>
     </row>
     <row r="945">
@@ -10867,7 +10867,7 @@
         </is>
       </c>
       <c r="C945" t="n">
-        <v>1139.078710004668</v>
+        <v>861.2399999999999</v>
       </c>
     </row>
     <row r="946">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="C946" t="n">
-        <v>1188.183508716269</v>
+        <v>747.91</v>
       </c>
     </row>
     <row r="947">
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="C947" t="n">
-        <v>1225.333065909951</v>
+        <v>839.36</v>
       </c>
     </row>
     <row r="948">
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="C948" t="n">
-        <v>1220.209733786153</v>
+        <v>781.52</v>
       </c>
     </row>
     <row r="949">
@@ -10911,7 +10911,7 @@
         </is>
       </c>
       <c r="C949" t="n">
-        <v>1199.353652579309</v>
+        <v>890.9600000000002</v>
       </c>
     </row>
     <row r="950">
@@ -10922,7 +10922,7 @@
         </is>
       </c>
       <c r="C950" t="n">
-        <v>1227.941125923946</v>
+        <v>916.6000000000001</v>
       </c>
     </row>
     <row r="951">
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="C951" t="n">
-        <v>1218.763922261756</v>
+        <v>824.11</v>
       </c>
     </row>
     <row r="952">
@@ -10944,7 +10944,7 @@
         </is>
       </c>
       <c r="C952" t="n">
-        <v>1208.923605042871</v>
+        <v>964.11</v>
       </c>
     </row>
     <row r="953">
@@ -10955,7 +10955,7 @@
         </is>
       </c>
       <c r="C953" t="n">
-        <v>1223.055762778577</v>
+        <v>992.8</v>
       </c>
     </row>
     <row r="954">
@@ -10966,7 +10966,7 @@
         </is>
       </c>
       <c r="C954" t="n">
-        <v>1244.054225424614</v>
+        <v>1014.08</v>
       </c>
     </row>
     <row r="955">
@@ -10977,7 +10977,7 @@
         </is>
       </c>
       <c r="C955" t="n">
-        <v>1274.135504037197</v>
+        <v>1000.84</v>
       </c>
     </row>
     <row r="956">
@@ -10988,7 +10988,7 @@
         </is>
       </c>
       <c r="C956" t="n">
-        <v>1260.654061474436</v>
+        <v>1079.99</v>
       </c>
     </row>
     <row r="957">
@@ -10999,7 +10999,7 @@
         </is>
       </c>
       <c r="C957" t="n">
-        <v>1292.476713082102</v>
+        <v>1133.02</v>
       </c>
     </row>
     <row r="958">
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="C958" t="n">
-        <v>1304.227981189941</v>
+        <v>1147.36</v>
       </c>
     </row>
     <row r="959">
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="C959" t="n">
-        <v>1348.488211438189</v>
+        <v>1202.34</v>
       </c>
     </row>
     <row r="960">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="C960" t="n">
-        <v>1336.579763820228</v>
+        <v>1229.07</v>
       </c>
     </row>
     <row r="961">
@@ -11043,7 +11043,7 @@
         </is>
       </c>
       <c r="C961" t="n">
-        <v>1355.881647631828</v>
+        <v>1215.73</v>
       </c>
     </row>
     <row r="962">
@@ -11058,7 +11058,7 @@
         </is>
       </c>
       <c r="C962" t="n">
-        <v>1084.803585295378</v>
+        <v>991.4</v>
       </c>
     </row>
     <row r="963">
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="C963" t="n">
-        <v>1092.545576051538</v>
+        <v>1144.17</v>
       </c>
     </row>
     <row r="964">
@@ -11080,7 +11080,7 @@
         </is>
       </c>
       <c r="C964" t="n">
-        <v>1106.320447029716</v>
+        <v>1001.01</v>
       </c>
     </row>
     <row r="965">
@@ -11091,7 +11091,7 @@
         </is>
       </c>
       <c r="C965" t="n">
-        <v>1097.586252283669</v>
+        <v>1139.28</v>
       </c>
     </row>
     <row r="966">
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="C966" t="n">
-        <v>1112.511973237353</v>
+        <v>1067.48</v>
       </c>
     </row>
     <row r="967">
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="C967" t="n">
-        <v>1133.617221962785</v>
+        <v>1128.16</v>
       </c>
     </row>
     <row r="968">
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="C968" t="n">
-        <v>1101.620726350711</v>
+        <v>1148.32</v>
       </c>
     </row>
     <row r="969">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="C969" t="n">
-        <v>1154.16354354981</v>
+        <v>1052.05</v>
       </c>
     </row>
     <row r="970">
@@ -11146,7 +11146,7 @@
         </is>
       </c>
       <c r="C970" t="n">
-        <v>1145.800300446607</v>
+        <v>1168.07</v>
       </c>
     </row>
     <row r="971">
@@ -11157,7 +11157,7 @@
         </is>
       </c>
       <c r="C971" t="n">
-        <v>1172.605139508304</v>
+        <v>1041.58</v>
       </c>
     </row>
     <row r="972">
@@ -11168,7 +11168,7 @@
         </is>
       </c>
       <c r="C972" t="n">
-        <v>1169.913157101076</v>
+        <v>1134.28</v>
       </c>
     </row>
     <row r="973">
@@ -11179,7 +11179,7 @@
         </is>
       </c>
       <c r="C973" t="n">
-        <v>1165.90567951478</v>
+        <v>1132.12</v>
       </c>
     </row>
     <row r="974">
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="C974" t="n">
-        <v>1184.200961213427</v>
+        <v>1036.24</v>
       </c>
     </row>
     <row r="975">
@@ -11201,7 +11201,7 @@
         </is>
       </c>
       <c r="C975" t="n">
-        <v>1173.988959113951</v>
+        <v>1148.03</v>
       </c>
     </row>
     <row r="976">
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="C976" t="n">
-        <v>1207.232292188628</v>
+        <v>1089.51</v>
       </c>
     </row>
     <row r="977">
@@ -11223,7 +11223,7 @@
         </is>
       </c>
       <c r="C977" t="n">
-        <v>1196.169734300709</v>
+        <v>1068.41</v>
       </c>
     </row>
     <row r="978">
@@ -11234,7 +11234,7 @@
         </is>
       </c>
       <c r="C978" t="n">
-        <v>1214.028072959135</v>
+        <v>1125.14</v>
       </c>
     </row>
     <row r="979">
@@ -11245,7 +11245,7 @@
         </is>
       </c>
       <c r="C979" t="n">
-        <v>1205.906798312988</v>
+        <v>1148.07</v>
       </c>
     </row>
     <row r="980">
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="C980" t="n">
-        <v>1229.546383329688</v>
+        <v>1166.14</v>
       </c>
     </row>
     <row r="981">
@@ -11267,7 +11267,7 @@
         </is>
       </c>
       <c r="C981" t="n">
-        <v>1210.445539977174</v>
+        <v>1183.57</v>
       </c>
     </row>
     <row r="982">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="C982" t="n">
-        <v>1087.123949479991</v>
+        <v>1158.64</v>
       </c>
     </row>
     <row r="983">
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="C983" t="n">
-        <v>1115.790545843506</v>
+        <v>1030.26</v>
       </c>
     </row>
     <row r="984">
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="C984" t="n">
-        <v>1067.558833316624</v>
+        <v>1072.86</v>
       </c>
     </row>
     <row r="985">
@@ -11311,7 +11311,7 @@
         </is>
       </c>
       <c r="C985" t="n">
-        <v>1050.021119528293</v>
+        <v>1087.33</v>
       </c>
     </row>
     <row r="986">
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="C986" t="n">
-        <v>981.332407103767</v>
+        <v>889.77</v>
       </c>
     </row>
     <row r="987">
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="C987" t="n">
-        <v>975.9674398127985</v>
+        <v>881.36</v>
       </c>
     </row>
     <row r="988">
@@ -11344,7 +11344,7 @@
         </is>
       </c>
       <c r="C988" t="n">
-        <v>951.0503546640068</v>
+        <v>904.08</v>
       </c>
     </row>
     <row r="989">
@@ -11355,7 +11355,7 @@
         </is>
       </c>
       <c r="C989" t="n">
-        <v>941.5212635404383</v>
+        <v>886.52</v>
       </c>
     </row>
     <row r="990">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="C990" t="n">
-        <v>645.6828289594774</v>
+        <v>521.9299999999999</v>
       </c>
     </row>
     <row r="991">
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="C991" t="n">
-        <v>244.0471860742346</v>
+        <v>231.98</v>
       </c>
     </row>
     <row r="992">
@@ -11388,7 +11388,7 @@
         </is>
       </c>
       <c r="C992" t="n">
-        <v>186.1947277052016</v>
+        <v>191.26</v>
       </c>
     </row>
     <row r="993">
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="C993" t="n">
-        <v>332.238689453492</v>
+        <v>414.45</v>
       </c>
     </row>
     <row r="994">
@@ -11410,7 +11410,7 @@
         </is>
       </c>
       <c r="C994" t="n">
-        <v>279.8415199344665</v>
+        <v>401.71</v>
       </c>
     </row>
     <row r="995">
@@ -11421,7 +11421,7 @@
         </is>
       </c>
       <c r="C995" t="n">
-        <v>0</v>
+        <v>147.34</v>
       </c>
     </row>
     <row r="996">
@@ -11432,7 +11432,7 @@
         </is>
       </c>
       <c r="C996" t="n">
-        <v>22.42974273141599</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="997">
@@ -11443,7 +11443,7 @@
         </is>
       </c>
       <c r="C997" t="n">
-        <v>89.09138607079072</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="998">
@@ -11454,7 +11454,7 @@
         </is>
       </c>
       <c r="C998" t="n">
-        <v>0</v>
+        <v>64.08</v>
       </c>
     </row>
     <row r="999">
@@ -11817,7 +11817,7 @@
         </is>
       </c>
       <c r="C1031" t="n">
-        <v>0</v>
+        <v>235.36</v>
       </c>
     </row>
     <row r="1032">
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="C1032" t="n">
-        <v>0</v>
+        <v>461.77</v>
       </c>
     </row>
     <row r="1033">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="C1033" t="n">
-        <v>0</v>
+        <v>375.91</v>
       </c>
     </row>
     <row r="1034">
@@ -11850,7 +11850,7 @@
         </is>
       </c>
       <c r="C1034" t="n">
-        <v>19.45246418198303</v>
+        <v>159.48</v>
       </c>
     </row>
     <row r="1035">
@@ -11861,7 +11861,7 @@
         </is>
       </c>
       <c r="C1035" t="n">
-        <v>153.1080408768284</v>
+        <v>147.27</v>
       </c>
     </row>
     <row r="1036">
@@ -11872,7 +11872,7 @@
         </is>
       </c>
       <c r="C1036" t="n">
-        <v>296.8942969390268</v>
+        <v>618.25</v>
       </c>
     </row>
     <row r="1037">
@@ -11883,7 +11883,7 @@
         </is>
       </c>
       <c r="C1037" t="n">
-        <v>458.5698876190259</v>
+        <v>433.26</v>
       </c>
     </row>
     <row r="1038">
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="C1038" t="n">
-        <v>575.2793400727521</v>
+        <v>820.89</v>
       </c>
     </row>
     <row r="1039">
@@ -11905,7 +11905,7 @@
         </is>
       </c>
       <c r="C1039" t="n">
-        <v>550.1519490060502</v>
+        <v>580.7</v>
       </c>
     </row>
     <row r="1040">
@@ -11916,7 +11916,7 @@
         </is>
       </c>
       <c r="C1040" t="n">
-        <v>573.1749477341066</v>
+        <v>790.9</v>
       </c>
     </row>
     <row r="1041">
@@ -11927,7 +11927,7 @@
         </is>
       </c>
       <c r="C1041" t="n">
-        <v>568.046282972137</v>
+        <v>586.04</v>
       </c>
     </row>
     <row r="1042">
@@ -11938,7 +11938,7 @@
         </is>
       </c>
       <c r="C1042" t="n">
-        <v>616.4256429184081</v>
+        <v>768.0700000000001</v>
       </c>
     </row>
     <row r="1043">
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="C1043" t="n">
-        <v>636.2433928151765</v>
+        <v>656.83</v>
       </c>
     </row>
     <row r="1044">
@@ -11960,7 +11960,7 @@
         </is>
       </c>
       <c r="C1044" t="n">
-        <v>670.5125921582021</v>
+        <v>633.13</v>
       </c>
     </row>
     <row r="1045">
@@ -11971,7 +11971,7 @@
         </is>
       </c>
       <c r="C1045" t="n">
-        <v>659.4986945936032</v>
+        <v>639.62</v>
       </c>
     </row>
     <row r="1046">
@@ -11982,7 +11982,7 @@
         </is>
       </c>
       <c r="C1046" t="n">
-        <v>632.2555793321401</v>
+        <v>508.47</v>
       </c>
     </row>
     <row r="1047">
@@ -11993,7 +11993,7 @@
         </is>
       </c>
       <c r="C1047" t="n">
-        <v>689.6131022208295</v>
+        <v>585.83</v>
       </c>
     </row>
     <row r="1048">
@@ -12004,7 +12004,7 @@
         </is>
       </c>
       <c r="C1048" t="n">
-        <v>707.1644808944767</v>
+        <v>481.33</v>
       </c>
     </row>
     <row r="1049">
@@ -12015,7 +12015,7 @@
         </is>
       </c>
       <c r="C1049" t="n">
-        <v>746.5713438263867</v>
+        <v>520.49</v>
       </c>
     </row>
     <row r="1050">
@@ -12026,7 +12026,7 @@
         </is>
       </c>
       <c r="C1050" t="n">
-        <v>769.889304103335</v>
+        <v>687.28</v>
       </c>
     </row>
     <row r="1051">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="C1051" t="n">
-        <v>845.6617597596584</v>
+        <v>547.4</v>
       </c>
     </row>
     <row r="1052">
@@ -12048,7 +12048,7 @@
         </is>
       </c>
       <c r="C1052" t="n">
-        <v>892.2880149068676</v>
+        <v>686.37</v>
       </c>
     </row>
     <row r="1053">
@@ -12059,7 +12059,7 @@
         </is>
       </c>
       <c r="C1053" t="n">
-        <v>930.6786769771165</v>
+        <v>762.78</v>
       </c>
     </row>
     <row r="1054">
@@ -12070,7 +12070,7 @@
         </is>
       </c>
       <c r="C1054" t="n">
-        <v>997.5062986795962</v>
+        <v>774.02</v>
       </c>
     </row>
     <row r="1055">
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="C1055" t="n">
-        <v>1025.150028383735</v>
+        <v>824.6900000000001</v>
       </c>
     </row>
     <row r="1056">
@@ -12092,7 +12092,7 @@
         </is>
       </c>
       <c r="C1056" t="n">
-        <v>1035.246378892855</v>
+        <v>992.3100000000001</v>
       </c>
     </row>
     <row r="1057">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="C1057" t="n">
-        <v>1096.021122980172</v>
+        <v>969.13</v>
       </c>
     </row>
     <row r="1058">
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="C1058" t="n">
-        <v>1090.940451961751</v>
+        <v>970.89</v>
       </c>
     </row>
     <row r="1059">
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="C1059" t="n">
-        <v>1094.863273917065</v>
+        <v>1087.96</v>
       </c>
     </row>
     <row r="1060">
@@ -12136,7 +12136,7 @@
         </is>
       </c>
       <c r="C1060" t="n">
-        <v>1105.105938686031</v>
+        <v>936.52</v>
       </c>
     </row>
     <row r="1061">
@@ -12147,7 +12147,7 @@
         </is>
       </c>
       <c r="C1061" t="n">
-        <v>1103.53014410619</v>
+        <v>1057.34</v>
       </c>
     </row>
     <row r="1062">
@@ -12158,7 +12158,7 @@
         </is>
       </c>
       <c r="C1062" t="n">
-        <v>1114.176422926804</v>
+        <v>942.0499999999998</v>
       </c>
     </row>
     <row r="1063">
@@ -12169,7 +12169,7 @@
         </is>
       </c>
       <c r="C1063" t="n">
-        <v>1128.928166560125</v>
+        <v>1100.88</v>
       </c>
     </row>
     <row r="1064">
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="C1064" t="n">
-        <v>1167.299497816999</v>
+        <v>928.39</v>
       </c>
     </row>
     <row r="1065">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="C1065" t="n">
-        <v>1148.638930403566</v>
+        <v>1092.62</v>
       </c>
     </row>
     <row r="1066">
@@ -12202,7 +12202,7 @@
         </is>
       </c>
       <c r="C1066" t="n">
-        <v>1193.365433201982</v>
+        <v>989.2500000000001</v>
       </c>
     </row>
     <row r="1067">
@@ -12213,7 +12213,7 @@
         </is>
       </c>
       <c r="C1067" t="n">
-        <v>1191.964615812162</v>
+        <v>1052.37</v>
       </c>
     </row>
     <row r="1068">
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="C1068" t="n">
-        <v>1212.319629004764</v>
+        <v>1077.03</v>
       </c>
     </row>
     <row r="1069">
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="C1069" t="n">
-        <v>1226.656426730322</v>
+        <v>997.3100000000001</v>
       </c>
     </row>
     <row r="1070">
@@ -12246,7 +12246,7 @@
         </is>
       </c>
       <c r="C1070" t="n">
-        <v>1242.450367836393</v>
+        <v>1115.91</v>
       </c>
     </row>
     <row r="1071">
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="C1071" t="n">
-        <v>1236.010207373984</v>
+        <v>996.28</v>
       </c>
     </row>
     <row r="1072">
@@ -12268,7 +12268,7 @@
         </is>
       </c>
       <c r="C1072" t="n">
-        <v>1251.217224991244</v>
+        <v>1136.25</v>
       </c>
     </row>
     <row r="1073">
@@ -12279,7 +12279,7 @@
         </is>
       </c>
       <c r="C1073" t="n">
-        <v>1247.297069355016</v>
+        <v>1013.06</v>
       </c>
     </row>
     <row r="1074">
@@ -12290,7 +12290,7 @@
         </is>
       </c>
       <c r="C1074" t="n">
-        <v>1267.470439559882</v>
+        <v>1123.04</v>
       </c>
     </row>
     <row r="1075">
@@ -12301,7 +12301,7 @@
         </is>
       </c>
       <c r="C1075" t="n">
-        <v>1262.813046696368</v>
+        <v>1055.45</v>
       </c>
     </row>
     <row r="1076">
@@ -12312,7 +12312,7 @@
         </is>
       </c>
       <c r="C1076" t="n">
-        <v>1264.915772585584</v>
+        <v>1103.57</v>
       </c>
     </row>
     <row r="1077">
@@ -12323,7 +12323,7 @@
         </is>
       </c>
       <c r="C1077" t="n">
-        <v>1258.1896494012</v>
+        <v>1034.33</v>
       </c>
     </row>
     <row r="1078">
@@ -12334,7 +12334,7 @@
         </is>
       </c>
       <c r="C1078" t="n">
-        <v>1201.028434255219</v>
+        <v>993.22</v>
       </c>
     </row>
     <row r="1079">
@@ -12345,7 +12345,7 @@
         </is>
       </c>
       <c r="C1079" t="n">
-        <v>1182.463521038997</v>
+        <v>1015.19</v>
       </c>
     </row>
     <row r="1080">
@@ -12356,7 +12356,7 @@
         </is>
       </c>
       <c r="C1080" t="n">
-        <v>1163.505992337357</v>
+        <v>919.1699999999998</v>
       </c>
     </row>
     <row r="1081">
@@ -12367,7 +12367,7 @@
         </is>
       </c>
       <c r="C1081" t="n">
-        <v>1118.756825826709</v>
+        <v>863.39</v>
       </c>
     </row>
     <row r="1082">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="C1082" t="n">
-        <v>1027.594376405849</v>
+        <v>806.99</v>
       </c>
     </row>
     <row r="1083">
@@ -12389,7 +12389,7 @@
         </is>
       </c>
       <c r="C1083" t="n">
-        <v>1007.330684641942</v>
+        <v>684.88</v>
       </c>
     </row>
     <row r="1084">
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="C1084" t="n">
-        <v>1003.292544386157</v>
+        <v>799.37</v>
       </c>
     </row>
     <row r="1085">
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="C1085" t="n">
-        <v>978.461114738004</v>
+        <v>591.25</v>
       </c>
     </row>
     <row r="1086">
@@ -12422,7 +12422,7 @@
         </is>
       </c>
       <c r="C1086" t="n">
-        <v>678.4698881805584</v>
+        <v>346.98</v>
       </c>
     </row>
     <row r="1087">
@@ -12433,7 +12433,7 @@
         </is>
       </c>
       <c r="C1087" t="n">
-        <v>294.3952893756496</v>
+        <v>139.81</v>
       </c>
     </row>
     <row r="1088">
@@ -12444,7 +12444,7 @@
         </is>
       </c>
       <c r="C1088" t="n">
-        <v>281.2613348477751</v>
+        <v>128.15</v>
       </c>
     </row>
     <row r="1089">
@@ -12455,7 +12455,7 @@
         </is>
       </c>
       <c r="C1089" t="n">
-        <v>412.4242364870726</v>
+        <v>316.19</v>
       </c>
     </row>
     <row r="1090">
@@ -12466,7 +12466,7 @@
         </is>
       </c>
       <c r="C1090" t="n">
-        <v>221.3214819242699</v>
+        <v>197.05</v>
       </c>
     </row>
     <row r="1091">
@@ -12477,7 +12477,7 @@
         </is>
       </c>
       <c r="C1091" t="n">
-        <v>0</v>
+        <v>76.84</v>
       </c>
     </row>
     <row r="1092">
@@ -12488,7 +12488,7 @@
         </is>
       </c>
       <c r="C1092" t="n">
-        <v>0</v>
+        <v>16.21</v>
       </c>
     </row>
     <row r="1093">
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>23.60025681018107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1094">
@@ -12873,7 +12873,7 @@
         </is>
       </c>
       <c r="C1127" t="n">
-        <v>0</v>
+        <v>333.42</v>
       </c>
     </row>
     <row r="1128">
@@ -12884,7 +12884,7 @@
         </is>
       </c>
       <c r="C1128" t="n">
-        <v>0</v>
+        <v>386.29</v>
       </c>
     </row>
     <row r="1129">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="C1129" t="n">
-        <v>0</v>
+        <v>266.03</v>
       </c>
     </row>
     <row r="1130">
@@ -12906,7 +12906,7 @@
         </is>
       </c>
       <c r="C1130" t="n">
-        <v>93.8324346956294</v>
+        <v>24.28</v>
       </c>
     </row>
     <row r="1131">
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="C1131" t="n">
-        <v>336.6364494960047</v>
+        <v>395.07</v>
       </c>
     </row>
     <row r="1132">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="C1132" t="n">
-        <v>418.3377989299909</v>
+        <v>240.69</v>
       </c>
     </row>
     <row r="1133">
@@ -12939,7 +12939,7 @@
         </is>
       </c>
       <c r="C1133" t="n">
-        <v>367.6187439857325</v>
+        <v>381.7</v>
       </c>
     </row>
     <row r="1134">
@@ -12950,7 +12950,7 @@
         </is>
       </c>
       <c r="C1134" t="n">
-        <v>381.0026659279221</v>
+        <v>597.5700000000001</v>
       </c>
     </row>
     <row r="1135">
@@ -12961,7 +12961,7 @@
         </is>
       </c>
       <c r="C1135" t="n">
-        <v>497.4778155919638</v>
+        <v>414.59</v>
       </c>
     </row>
     <row r="1136">
@@ -12972,7 +12972,7 @@
         </is>
       </c>
       <c r="C1136" t="n">
-        <v>578.494254310727</v>
+        <v>666.28</v>
       </c>
     </row>
     <row r="1137">
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="C1137" t="n">
-        <v>613.3800399423957</v>
+        <v>395.07</v>
       </c>
     </row>
     <row r="1138">
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="C1138" t="n">
-        <v>655.0619396344572</v>
+        <v>699.35</v>
       </c>
     </row>
     <row r="1139">
@@ -13005,7 +13005,7 @@
         </is>
       </c>
       <c r="C1139" t="n">
-        <v>680.3916376618114</v>
+        <v>573.23</v>
       </c>
     </row>
     <row r="1140">
@@ -13016,7 +13016,7 @@
         </is>
       </c>
       <c r="C1140" t="n">
-        <v>641.1477534840344</v>
+        <v>639.55</v>
       </c>
     </row>
     <row r="1141">
@@ -13027,7 +13027,7 @@
         </is>
       </c>
       <c r="C1141" t="n">
-        <v>637.9984973535526</v>
+        <v>660.53</v>
       </c>
     </row>
     <row r="1142">
@@ -13038,7 +13038,7 @@
         </is>
       </c>
       <c r="C1142" t="n">
-        <v>676.1548566341171</v>
+        <v>502.61</v>
       </c>
     </row>
     <row r="1143">
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="C1143" t="n">
-        <v>687.6186955444828</v>
+        <v>631</v>
       </c>
     </row>
     <row r="1144">
@@ -13060,7 +13060,7 @@
         </is>
       </c>
       <c r="C1144" t="n">
-        <v>668.3038800853158</v>
+        <v>444.31</v>
       </c>
     </row>
     <row r="1145">
@@ -13071,7 +13071,7 @@
         </is>
       </c>
       <c r="C1145" t="n">
-        <v>683.8885151431332</v>
+        <v>504.45</v>
       </c>
     </row>
     <row r="1146">
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="C1146" t="n">
-        <v>709.3281988327863</v>
+        <v>503.36</v>
       </c>
     </row>
     <row r="1147">
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="C1147" t="n">
-        <v>723.8493058651655</v>
+        <v>477.44</v>
       </c>
     </row>
     <row r="1148">
@@ -13104,7 +13104,7 @@
         </is>
       </c>
       <c r="C1148" t="n">
-        <v>780.855874504157</v>
+        <v>658.99</v>
       </c>
     </row>
     <row r="1149">
@@ -13115,7 +13115,7 @@
         </is>
       </c>
       <c r="C1149" t="n">
-        <v>813.1466650853517</v>
+        <v>463.16</v>
       </c>
     </row>
     <row r="1150">
@@ -13126,7 +13126,7 @@
         </is>
       </c>
       <c r="C1150" t="n">
-        <v>920.0897240168531</v>
+        <v>786.1799999999999</v>
       </c>
     </row>
     <row r="1151">
@@ -13137,7 +13137,7 @@
         </is>
       </c>
       <c r="C1151" t="n">
-        <v>939.8174856444684</v>
+        <v>721.77</v>
       </c>
     </row>
     <row r="1152">
@@ -13148,7 +13148,7 @@
         </is>
       </c>
       <c r="C1152" t="n">
-        <v>960.1851638527294</v>
+        <v>819.05</v>
       </c>
     </row>
     <row r="1153">
@@ -13159,7 +13159,7 @@
         </is>
       </c>
       <c r="C1153" t="n">
-        <v>1001.840067064045</v>
+        <v>934.3</v>
       </c>
     </row>
     <row r="1154">
@@ -15281,7 +15281,7 @@
     <row r="1346">
       <c r="A1346" s="1" t="inlineStr">
         <is>
-          <t>rp08</t>
+          <t>rp_design</t>
         </is>
       </c>
       <c r="B1346" s="1" t="inlineStr">
@@ -15290,7 +15290,7 @@
         </is>
       </c>
       <c r="C1346" t="n">
-        <v>1013.221726211152</v>
+        <v>1546.1</v>
       </c>
     </row>
     <row r="1347">
@@ -15301,7 +15301,7 @@
         </is>
       </c>
       <c r="C1347" t="n">
-        <v>992.9267528108256</v>
+        <v>1517.97</v>
       </c>
     </row>
     <row r="1348">
@@ -15312,7 +15312,7 @@
         </is>
       </c>
       <c r="C1348" t="n">
-        <v>1042.295555202216</v>
+        <v>1482.27</v>
       </c>
     </row>
     <row r="1349">
@@ -15323,7 +15323,7 @@
         </is>
       </c>
       <c r="C1349" t="n">
-        <v>1000.551949268449</v>
+        <v>1433.13</v>
       </c>
     </row>
     <row r="1350">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="C1350" t="n">
-        <v>1031.159387862387</v>
+        <v>1519.32</v>
       </c>
     </row>
     <row r="1351">
@@ -15345,7 +15345,7 @@
         </is>
       </c>
       <c r="C1351" t="n">
-        <v>1006.157409018409</v>
+        <v>1568.81</v>
       </c>
     </row>
     <row r="1352">
@@ -15356,7 +15356,7 @@
         </is>
       </c>
       <c r="C1352" t="n">
-        <v>1032.234009679737</v>
+        <v>1535.21</v>
       </c>
     </row>
     <row r="1353">
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="C1353" t="n">
-        <v>993.7875929728854</v>
+        <v>1525.04</v>
       </c>
     </row>
     <row r="1354">
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="C1354" t="n">
-        <v>1016.086590843404</v>
+        <v>1543.94</v>
       </c>
     </row>
     <row r="1355">
@@ -15389,7 +15389,7 @@
         </is>
       </c>
       <c r="C1355" t="n">
-        <v>1011.111048977518</v>
+        <v>1551.65</v>
       </c>
     </row>
     <row r="1356">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="C1356" t="n">
-        <v>1015.056248968019</v>
+        <v>1552.6</v>
       </c>
     </row>
     <row r="1357">
@@ -15411,7 +15411,7 @@
         </is>
       </c>
       <c r="C1357" t="n">
-        <v>1010.227354651863</v>
+        <v>1548.04</v>
       </c>
     </row>
     <row r="1358">
@@ -15422,7 +15422,7 @@
         </is>
       </c>
       <c r="C1358" t="n">
-        <v>1021.708715087652</v>
+        <v>1552.61</v>
       </c>
     </row>
     <row r="1359">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="C1359" t="n">
-        <v>1014.053046411902</v>
+        <v>1529.96</v>
       </c>
     </row>
     <row r="1360">
@@ -15444,7 +15444,7 @@
         </is>
       </c>
       <c r="C1360" t="n">
-        <v>1019.539474059807</v>
+        <v>1419.68</v>
       </c>
     </row>
     <row r="1361">
@@ -15455,7 +15455,7 @@
         </is>
       </c>
       <c r="C1361" t="n">
-        <v>1017.256438342398</v>
+        <v>1521.68</v>
       </c>
     </row>
     <row r="1362">
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="C1362" t="n">
-        <v>1018.541032787772</v>
+        <v>1605.06</v>
       </c>
     </row>
     <row r="1363">
@@ -15477,7 +15477,7 @@
         </is>
       </c>
       <c r="C1363" t="n">
-        <v>999.5911221406641</v>
+        <v>1581.19</v>
       </c>
     </row>
     <row r="1364">
@@ -15488,7 +15488,7 @@
         </is>
       </c>
       <c r="C1364" t="n">
-        <v>1037.69948767768</v>
+        <v>1550.53</v>
       </c>
     </row>
     <row r="1365">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="C1365" t="n">
-        <v>994.7236614234432</v>
+        <v>1534.3</v>
       </c>
     </row>
     <row r="1366">
@@ -15510,7 +15510,7 @@
         </is>
       </c>
       <c r="C1366" t="n">
-        <v>927.5614642885079</v>
+        <v>1545.11</v>
       </c>
     </row>
     <row r="1367">
@@ -15521,7 +15521,7 @@
         </is>
       </c>
       <c r="C1367" t="n">
-        <v>956.1148849293895</v>
+        <v>1552.27</v>
       </c>
     </row>
     <row r="1368">
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="C1368" t="n">
-        <v>906.7970282776782</v>
+        <v>1558.01</v>
       </c>
     </row>
     <row r="1369">
@@ -15543,7 +15543,7 @@
         </is>
       </c>
       <c r="C1369" t="n">
-        <v>903.7026697526642</v>
+        <v>1549.73</v>
       </c>
     </row>
     <row r="1370">
@@ -15554,7 +15554,7 @@
         </is>
       </c>
       <c r="C1370" t="n">
-        <v>705.5670700849026</v>
+        <v>1530.47</v>
       </c>
     </row>
     <row r="1371">
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="C1371" t="n">
-        <v>725.7244423752536</v>
+        <v>1475.02</v>
       </c>
     </row>
     <row r="1372">
@@ -15576,7 +15576,7 @@
         </is>
       </c>
       <c r="C1372" t="n">
-        <v>715.5576724745578</v>
+        <v>1448.58</v>
       </c>
     </row>
     <row r="1373">
@@ -15587,7 +15587,7 @@
         </is>
       </c>
       <c r="C1373" t="n">
-        <v>648.3569089385567</v>
+        <v>1369.75</v>
       </c>
     </row>
     <row r="1374">
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="C1374" t="n">
-        <v>257.8925716696698</v>
+        <v>1338.83</v>
       </c>
     </row>
     <row r="1375">
@@ -15609,7 +15609,7 @@
         </is>
       </c>
       <c r="C1375" t="n">
-        <v>0</v>
+        <v>1332.08</v>
       </c>
     </row>
     <row r="1376">
@@ -15620,7 +15620,7 @@
         </is>
       </c>
       <c r="C1376" t="n">
-        <v>0</v>
+        <v>1363.78</v>
       </c>
     </row>
     <row r="1377">
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="C1377" t="n">
-        <v>45.19791753539388</v>
+        <v>1432.54</v>
       </c>
     </row>
     <row r="1378">
@@ -15642,7 +15642,7 @@
         </is>
       </c>
       <c r="C1378" t="n">
-        <v>71.74445693563287</v>
+        <v>1420.89</v>
       </c>
     </row>
     <row r="1379">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="C1379" t="n">
-        <v>0</v>
+        <v>1264.12</v>
       </c>
     </row>
     <row r="1380">
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="C1380" t="n">
-        <v>0</v>
+        <v>983.41</v>
       </c>
     </row>
     <row r="1381">
@@ -15675,7 +15675,7 @@
         </is>
       </c>
       <c r="C1381" t="n">
-        <v>0</v>
+        <v>909.21</v>
       </c>
     </row>
     <row r="1382">
@@ -15686,7 +15686,7 @@
         </is>
       </c>
       <c r="C1382" t="n">
-        <v>0</v>
+        <v>1199.35</v>
       </c>
     </row>
     <row r="1383">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="C1383" t="n">
-        <v>0</v>
+        <v>1431.16</v>
       </c>
     </row>
     <row r="1384">
@@ -15708,7 +15708,7 @@
         </is>
       </c>
       <c r="C1384" t="n">
-        <v>0</v>
+        <v>1400.81</v>
       </c>
     </row>
     <row r="1385">
@@ -15719,7 +15719,7 @@
         </is>
       </c>
       <c r="C1385" t="n">
-        <v>0</v>
+        <v>1277.91</v>
       </c>
     </row>
     <row r="1386">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="C1386" t="n">
-        <v>0</v>
+        <v>1251.87</v>
       </c>
     </row>
     <row r="1387">
@@ -15741,7 +15741,7 @@
         </is>
       </c>
       <c r="C1387" t="n">
-        <v>0</v>
+        <v>1219.43</v>
       </c>
     </row>
     <row r="1388">
@@ -15752,7 +15752,7 @@
         </is>
       </c>
       <c r="C1388" t="n">
-        <v>0</v>
+        <v>1095.55</v>
       </c>
     </row>
     <row r="1389">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="C1389" t="n">
-        <v>0</v>
+        <v>1070.84</v>
       </c>
     </row>
     <row r="1390">
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="C1390" t="n">
-        <v>0</v>
+        <v>1074.33</v>
       </c>
     </row>
     <row r="1391">
@@ -15785,7 +15785,7 @@
         </is>
       </c>
       <c r="C1391" t="n">
-        <v>0</v>
+        <v>1084.9</v>
       </c>
     </row>
     <row r="1392">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="C1392" t="n">
-        <v>0</v>
+        <v>1111.99</v>
       </c>
     </row>
     <row r="1393">
@@ -15807,7 +15807,7 @@
         </is>
       </c>
       <c r="C1393" t="n">
-        <v>0</v>
+        <v>1167.58</v>
       </c>
     </row>
     <row r="1394">
@@ -15818,7 +15818,7 @@
         </is>
       </c>
       <c r="C1394" t="n">
-        <v>0</v>
+        <v>1160.3</v>
       </c>
     </row>
     <row r="1395">
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="C1395" t="n">
-        <v>0</v>
+        <v>1080.48</v>
       </c>
     </row>
     <row r="1396">
@@ -15840,7 +15840,7 @@
         </is>
       </c>
       <c r="C1396" t="n">
-        <v>0</v>
+        <v>997.61</v>
       </c>
     </row>
     <row r="1397">
@@ -15851,7 +15851,7 @@
         </is>
       </c>
       <c r="C1397" t="n">
-        <v>0</v>
+        <v>1059.14</v>
       </c>
     </row>
     <row r="1398">
@@ -15862,7 +15862,7 @@
         </is>
       </c>
       <c r="C1398" t="n">
-        <v>0</v>
+        <v>1250.7</v>
       </c>
     </row>
     <row r="1399">
@@ -15873,7 +15873,7 @@
         </is>
       </c>
       <c r="C1399" t="n">
-        <v>0</v>
+        <v>1338.64</v>
       </c>
     </row>
     <row r="1400">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="C1400" t="n">
-        <v>0</v>
+        <v>1328.44</v>
       </c>
     </row>
     <row r="1401">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="C1401" t="n">
-        <v>0</v>
+        <v>1268.54</v>
       </c>
     </row>
     <row r="1402">
@@ -15906,7 +15906,7 @@
         </is>
       </c>
       <c r="C1402" t="n">
-        <v>0</v>
+        <v>1203.88</v>
       </c>
     </row>
     <row r="1403">
@@ -15917,7 +15917,7 @@
         </is>
       </c>
       <c r="C1403" t="n">
-        <v>0</v>
+        <v>1158.69</v>
       </c>
     </row>
     <row r="1404">
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="C1404" t="n">
-        <v>0</v>
+        <v>1174.1</v>
       </c>
     </row>
     <row r="1405">
@@ -15939,7 +15939,7 @@
         </is>
       </c>
       <c r="C1405" t="n">
-        <v>0</v>
+        <v>1221.36</v>
       </c>
     </row>
     <row r="1406">
@@ -15950,7 +15950,7 @@
         </is>
       </c>
       <c r="C1406" t="n">
-        <v>0</v>
+        <v>1292.6</v>
       </c>
     </row>
     <row r="1407">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="C1407" t="n">
-        <v>0</v>
+        <v>1317.94</v>
       </c>
     </row>
     <row r="1408">
@@ -15972,7 +15972,7 @@
         </is>
       </c>
       <c r="C1408" t="n">
-        <v>63.6693191322421</v>
+        <v>1326.66</v>
       </c>
     </row>
     <row r="1409">
@@ -15983,7 +15983,7 @@
         </is>
       </c>
       <c r="C1409" t="n">
-        <v>68.48678636659984</v>
+        <v>1332.39</v>
       </c>
     </row>
     <row r="1410">
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="C1410" t="n">
-        <v>0</v>
+        <v>1189.41</v>
       </c>
     </row>
     <row r="1411">
@@ -16005,7 +16005,7 @@
         </is>
       </c>
       <c r="C1411" t="n">
-        <v>0</v>
+        <v>1071.72</v>
       </c>
     </row>
     <row r="1412">
@@ -16016,7 +16016,7 @@
         </is>
       </c>
       <c r="C1412" t="n">
-        <v>0</v>
+        <v>1070.71</v>
       </c>
     </row>
     <row r="1413">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="C1413" t="n">
-        <v>0</v>
+        <v>1120.97</v>
       </c>
     </row>
     <row r="1414">
@@ -16038,7 +16038,7 @@
         </is>
       </c>
       <c r="C1414" t="n">
-        <v>55.4113480200953</v>
+        <v>1241.98</v>
       </c>
     </row>
     <row r="1415">
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="C1415" t="n">
-        <v>124.3780718221797</v>
+        <v>1299.38</v>
       </c>
     </row>
     <row r="1416">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="C1416" t="n">
-        <v>92.91883950593918</v>
+        <v>1294.9</v>
       </c>
     </row>
     <row r="1417">
@@ -16071,7 +16071,7 @@
         </is>
       </c>
       <c r="C1417" t="n">
-        <v>134.7114866657522</v>
+        <v>1263.74</v>
       </c>
     </row>
     <row r="1418">
@@ -16082,7 +16082,7 @@
         </is>
       </c>
       <c r="C1418" t="n">
-        <v>452.0558320276621</v>
+        <v>1461.27</v>
       </c>
     </row>
     <row r="1419">
@@ -16093,7 +16093,7 @@
         </is>
       </c>
       <c r="C1419" t="n">
-        <v>647.3032367711684</v>
+        <v>1581.47</v>
       </c>
     </row>
     <row r="1420">
@@ -16104,7 +16104,7 @@
         </is>
       </c>
       <c r="C1420" t="n">
-        <v>639.5161566547501</v>
+        <v>1536.92</v>
       </c>
     </row>
     <row r="1421">
@@ -16115,7 +16115,7 @@
         </is>
       </c>
       <c r="C1421" t="n">
-        <v>558.7181180368368</v>
+        <v>1499.86</v>
       </c>
     </row>
     <row r="1422">
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="C1422" t="n">
-        <v>569.6966868735458</v>
+        <v>1449.19</v>
       </c>
     </row>
     <row r="1423">
@@ -16137,7 +16137,7 @@
         </is>
       </c>
       <c r="C1423" t="n">
-        <v>673.9445257246431</v>
+        <v>1395.69</v>
       </c>
     </row>
     <row r="1424">
@@ -16148,7 +16148,7 @@
         </is>
       </c>
       <c r="C1424" t="n">
-        <v>720.4537008962715</v>
+        <v>1369.51</v>
       </c>
     </row>
     <row r="1425">
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="C1425" t="n">
-        <v>642.640511269482</v>
+        <v>1357.06</v>
       </c>
     </row>
     <row r="1426">
@@ -16170,7 +16170,7 @@
         </is>
       </c>
       <c r="C1426" t="n">
-        <v>666.6930900674708</v>
+        <v>1437.62</v>
       </c>
     </row>
     <row r="1427">
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="C1427" t="n">
-        <v>728.4964619679035</v>
+        <v>1485.34</v>
       </c>
     </row>
     <row r="1428">
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="C1428" t="n">
-        <v>694.4137621223774</v>
+        <v>1483.72</v>
       </c>
     </row>
     <row r="1429">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="C1429" t="n">
-        <v>727.0047516649539</v>
+        <v>1467.09</v>
       </c>
     </row>
     <row r="1430">
@@ -16214,7 +16214,7 @@
         </is>
       </c>
       <c r="C1430" t="n">
-        <v>735.8431233067195</v>
+        <v>1437.58</v>
       </c>
     </row>
     <row r="1431">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="C1431" t="n">
-        <v>721.6921108860486</v>
+        <v>1369.32</v>
       </c>
     </row>
     <row r="1432">
@@ -16236,7 +16236,7 @@
         </is>
       </c>
       <c r="C1432" t="n">
-        <v>753.8403010089817</v>
+        <v>1393.47</v>
       </c>
     </row>
     <row r="1433">
@@ -16247,7 +16247,7 @@
         </is>
       </c>
       <c r="C1433" t="n">
-        <v>732.9049348996011</v>
+        <v>1454.3</v>
       </c>
     </row>
     <row r="1434">
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="C1434" t="n">
-        <v>819.502693658028</v>
+        <v>1483.97</v>
       </c>
     </row>
     <row r="1435">
@@ -16269,7 +16269,7 @@
         </is>
       </c>
       <c r="C1435" t="n">
-        <v>749.8132069322673</v>
+        <v>1488.05</v>
       </c>
     </row>
     <row r="1436">
@@ -16280,7 +16280,7 @@
         </is>
       </c>
       <c r="C1436" t="n">
-        <v>799.8866793678216</v>
+        <v>1466.32</v>
       </c>
     </row>
     <row r="1437">
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="C1437" t="n">
-        <v>843.9823596381888</v>
+        <v>1445.37</v>
       </c>
     </row>
     <row r="1438">
@@ -16302,7 +16302,7 @@
         </is>
       </c>
       <c r="C1438" t="n">
-        <v>918.4555084813239</v>
+        <v>1419.69</v>
       </c>
     </row>
     <row r="1439">
@@ -16313,7 +16313,7 @@
         </is>
       </c>
       <c r="C1439" t="n">
-        <v>886.8458195880858</v>
+        <v>1480.44</v>
       </c>
     </row>
     <row r="1440">
@@ -16324,7 +16324,7 @@
         </is>
       </c>
       <c r="C1440" t="n">
-        <v>952.5286857586854</v>
+        <v>1514.42</v>
       </c>
     </row>
     <row r="1441">
@@ -16335,7 +16335,7 @@
         </is>
       </c>
       <c r="C1441" t="n">
-        <v>953.6047359612598</v>
+        <v>1503.46</v>
       </c>
     </row>
     <row r="1442">
@@ -16346,7 +16346,7 @@
         </is>
       </c>
       <c r="C1442" t="n">
-        <v>957.3590084600648</v>
+        <v>1480.33</v>
       </c>
     </row>
     <row r="1443">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="C1443" t="n">
-        <v>967.1010718206298</v>
+        <v>1448.24</v>
       </c>
     </row>
     <row r="1444">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="C1444" t="n">
-        <v>971.1800638938405</v>
+        <v>1442.12</v>
       </c>
     </row>
     <row r="1445">
@@ -16379,7 +16379,7 @@
         </is>
       </c>
       <c r="C1445" t="n">
-        <v>979.7122849691212</v>
+        <v>1411.29</v>
       </c>
     </row>
     <row r="1446">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="C1446" t="n">
-        <v>969.2526960973704</v>
+        <v>1450.44</v>
       </c>
     </row>
     <row r="1447">
@@ -16401,7 +16401,7 @@
         </is>
       </c>
       <c r="C1447" t="n">
-        <v>970.1644819991097</v>
+        <v>1497.94</v>
       </c>
     </row>
     <row r="1448">
@@ -16412,7 +16412,7 @@
         </is>
       </c>
       <c r="C1448" t="n">
-        <v>964.5114094083278</v>
+        <v>1504.26</v>
       </c>
     </row>
     <row r="1449">
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="C1449" t="n">
-        <v>972.5922607526171</v>
+        <v>1487.68</v>
       </c>
     </row>
     <row r="1450">
@@ -16434,7 +16434,7 @@
         </is>
       </c>
       <c r="C1450" t="n">
-        <v>954.7422067284946</v>
+        <v>1471.26</v>
       </c>
     </row>
     <row r="1451">
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="C1451" t="n">
-        <v>961.4022909026594</v>
+        <v>1452.63</v>
       </c>
     </row>
     <row r="1452">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="C1452" t="n">
-        <v>973.5673717326491</v>
+        <v>1409.9</v>
       </c>
     </row>
     <row r="1453">
@@ -16467,7 +16467,7 @@
         </is>
       </c>
       <c r="C1453" t="n">
-        <v>963.3853657228906</v>
+        <v>1450.93</v>
       </c>
     </row>
     <row r="1454">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="C1454" t="n">
-        <v>989.5076747114065</v>
+        <v>1473.31</v>
       </c>
     </row>
     <row r="1455">
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="C1455" t="n">
-        <v>968.2942496116261</v>
+        <v>1475.4</v>
       </c>
     </row>
     <row r="1456">
@@ -16500,7 +16500,7 @@
         </is>
       </c>
       <c r="C1456" t="n">
-        <v>991.9130754297278</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="1457">
@@ -16511,7 +16511,7 @@
         </is>
       </c>
       <c r="C1457" t="n">
-        <v>962.1907595466695</v>
+        <v>1451.54</v>
       </c>
     </row>
     <row r="1458">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="C1458" t="n">
-        <v>990.564203649244</v>
+        <v>1407.51</v>
       </c>
     </row>
     <row r="1459">
@@ -16533,7 +16533,7 @@
         </is>
       </c>
       <c r="C1459" t="n">
-        <v>974.5020117979828</v>
+        <v>1406.57</v>
       </c>
     </row>
     <row r="1460">
@@ -16544,7 +16544,7 @@
         </is>
       </c>
       <c r="C1460" t="n">
-        <v>988.3316375431058</v>
+        <v>1463.98</v>
       </c>
     </row>
     <row r="1461">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="C1461" t="n">
-        <v>982.862350517897</v>
+        <v>1492.31</v>
       </c>
     </row>
     <row r="1462">
@@ -16566,7 +16566,7 @@
         </is>
       </c>
       <c r="C1462" t="n">
-        <v>883.2548591333001</v>
+        <v>1452.24</v>
       </c>
     </row>
     <row r="1463">
@@ -16577,7 +16577,7 @@
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>934.5567428620585</v>
+        <v>1391.97</v>
       </c>
     </row>
     <row r="1464">
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>862.1428493844701</v>
+        <v>1366.06</v>
       </c>
     </row>
     <row r="1465">
@@ -16599,7 +16599,7 @@
         </is>
       </c>
       <c r="C1465" t="n">
-        <v>833.1571041489265</v>
+        <v>1336.9</v>
       </c>
     </row>
     <row r="1466">
@@ -16610,7 +16610,7 @@
         </is>
       </c>
       <c r="C1466" t="n">
-        <v>682.2139239185872</v>
+        <v>1357.15</v>
       </c>
     </row>
     <row r="1467">
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="C1467" t="n">
-        <v>718.1559051982076</v>
+        <v>1343.06</v>
       </c>
     </row>
     <row r="1468">
@@ -16632,7 +16632,7 @@
         </is>
       </c>
       <c r="C1468" t="n">
-        <v>716.9765351310497</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="1469">
@@ -16643,7 +16643,7 @@
         </is>
       </c>
       <c r="C1469" t="n">
-        <v>610.1914079925546</v>
+        <v>1325.21</v>
       </c>
     </row>
     <row r="1470">
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="C1470" t="n">
-        <v>235.2445716759264</v>
+        <v>1164.77</v>
       </c>
     </row>
     <row r="1471">
@@ -16665,7 +16665,7 @@
         </is>
       </c>
       <c r="C1471" t="n">
-        <v>0</v>
+        <v>944.22</v>
       </c>
     </row>
     <row r="1472">
@@ -16676,7 +16676,7 @@
         </is>
       </c>
       <c r="C1472" t="n">
-        <v>0</v>
+        <v>880.88</v>
       </c>
     </row>
     <row r="1473">
@@ -16687,7 +16687,7 @@
         </is>
       </c>
       <c r="C1473" t="n">
-        <v>116.7976314349283</v>
+        <v>862.0700000000001</v>
       </c>
     </row>
     <row r="1474">
@@ -16698,7 +16698,7 @@
         </is>
       </c>
       <c r="C1474" t="n">
-        <v>143.347979862433</v>
+        <v>826.5</v>
       </c>
     </row>
     <row r="1475">
@@ -16709,7 +16709,7 @@
         </is>
       </c>
       <c r="C1475" t="n">
-        <v>0</v>
+        <v>795.53</v>
       </c>
     </row>
     <row r="1476">
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="C1476" t="n">
-        <v>0</v>
+        <v>746.65</v>
       </c>
     </row>
     <row r="1477">
@@ -16731,7 +16731,7 @@
         </is>
       </c>
       <c r="C1477" t="n">
-        <v>163.1772996795212</v>
+        <v>750.39</v>
       </c>
     </row>
     <row r="1478">
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="C1478" t="n">
-        <v>0</v>
+        <v>653.37</v>
       </c>
     </row>
     <row r="1479">
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="C1479" t="n">
-        <v>0</v>
+        <v>582.21</v>
       </c>
     </row>
     <row r="1480">
@@ -16764,7 +16764,7 @@
         </is>
       </c>
       <c r="C1480" t="n">
-        <v>0</v>
+        <v>637.42</v>
       </c>
     </row>
     <row r="1481">
@@ -16775,7 +16775,7 @@
         </is>
       </c>
       <c r="C1481" t="n">
-        <v>0</v>
+        <v>401.97</v>
       </c>
     </row>
     <row r="1482">
@@ -16786,7 +16786,7 @@
         </is>
       </c>
       <c r="C1482" t="n">
-        <v>259.8646955365121</v>
+        <v>671.52</v>
       </c>
     </row>
     <row r="1483">
@@ -16797,7 +16797,7 @@
         </is>
       </c>
       <c r="C1483" t="n">
-        <v>395.9036282043784</v>
+        <v>810.92</v>
       </c>
     </row>
     <row r="1484">
@@ -16808,7 +16808,7 @@
         </is>
       </c>
       <c r="C1484" t="n">
-        <v>288.0767321087005</v>
+        <v>779.8099999999999</v>
       </c>
     </row>
     <row r="1485">
@@ -16819,7 +16819,7 @@
         </is>
       </c>
       <c r="C1485" t="n">
-        <v>166.6468473902116</v>
+        <v>705.78</v>
       </c>
     </row>
     <row r="1486">
@@ -16830,7 +16830,7 @@
         </is>
       </c>
       <c r="C1486" t="n">
-        <v>337.7931082380908</v>
+        <v>671.6900000000001</v>
       </c>
     </row>
     <row r="1487">
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="C1487" t="n">
-        <v>500.700443110152</v>
+        <v>802.0700000000001</v>
       </c>
     </row>
     <row r="1488">
@@ -16852,7 +16852,7 @@
         </is>
       </c>
       <c r="C1488" t="n">
-        <v>444.2397080783423</v>
+        <v>756.41</v>
       </c>
     </row>
     <row r="1489">
@@ -16863,7 +16863,7 @@
         </is>
       </c>
       <c r="C1489" t="n">
-        <v>481.9833592546627</v>
+        <v>856.76</v>
       </c>
     </row>
     <row r="1490">
@@ -16874,7 +16874,7 @@
         </is>
       </c>
       <c r="C1490" t="n">
-        <v>601.7253687660161</v>
+        <v>887.6</v>
       </c>
     </row>
     <row r="1491">
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="C1491" t="n">
-        <v>614.8022354977453</v>
+        <v>983.01</v>
       </c>
     </row>
     <row r="1492">
@@ -16896,7 +16896,7 @@
         </is>
       </c>
       <c r="C1492" t="n">
-        <v>504.5294677690475</v>
+        <v>1063.45</v>
       </c>
     </row>
     <row r="1493">
@@ -16907,7 +16907,7 @@
         </is>
       </c>
       <c r="C1493" t="n">
-        <v>566.5266239316251</v>
+        <v>1088.17</v>
       </c>
     </row>
     <row r="1494">
@@ -16918,7 +16918,7 @@
         </is>
       </c>
       <c r="C1494" t="n">
-        <v>603.2161268121492</v>
+        <v>1059.3</v>
       </c>
     </row>
     <row r="1495">
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="C1495" t="n">
-        <v>492.1358453031121</v>
+        <v>1009.98</v>
       </c>
     </row>
     <row r="1496">
@@ -16940,7 +16940,7 @@
         </is>
       </c>
       <c r="C1496" t="n">
-        <v>556.8407437232302</v>
+        <v>861.78</v>
       </c>
     </row>
     <row r="1497">
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="C1497" t="n">
-        <v>501.710311463984</v>
+        <v>986.24</v>
       </c>
     </row>
     <row r="1498">
@@ -16962,7 +16962,7 @@
         </is>
       </c>
       <c r="C1498" t="n">
-        <v>304.4122216662792</v>
+        <v>819.67</v>
       </c>
     </row>
     <row r="1499">
@@ -16973,7 +16973,7 @@
         </is>
       </c>
       <c r="C1499" t="n">
-        <v>220.1517772637988</v>
+        <v>790.4</v>
       </c>
     </row>
     <row r="1500">
@@ -16984,7 +16984,7 @@
         </is>
       </c>
       <c r="C1500" t="n">
-        <v>245.1251884032827</v>
+        <v>805.35</v>
       </c>
     </row>
     <row r="1501">
@@ -16995,7 +16995,7 @@
         </is>
       </c>
       <c r="C1501" t="n">
-        <v>210.2930624432204</v>
+        <v>796.36</v>
       </c>
     </row>
     <row r="1502">
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="C1502" t="n">
-        <v>228.6487648368714</v>
+        <v>845.62</v>
       </c>
     </row>
     <row r="1503">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="C1503" t="n">
-        <v>314.000019422581</v>
+        <v>819.35</v>
       </c>
     </row>
     <row r="1504">
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="C1504" t="n">
-        <v>370.4717054077796</v>
+        <v>940.5</v>
       </c>
     </row>
     <row r="1505">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="C1505" t="n">
-        <v>437.3215623069232</v>
+        <v>972.72</v>
       </c>
     </row>
     <row r="1506">
@@ -17050,7 +17050,7 @@
         </is>
       </c>
       <c r="C1506" t="n">
-        <v>227.4613005867737</v>
+        <v>642.52</v>
       </c>
     </row>
     <row r="1507">
@@ -17061,7 +17061,7 @@
         </is>
       </c>
       <c r="C1507" t="n">
-        <v>18.35951142091679</v>
+        <v>527.9299999999999</v>
       </c>
     </row>
     <row r="1508">
@@ -17072,7 +17072,7 @@
         </is>
       </c>
       <c r="C1508" t="n">
-        <v>83.74432120797117</v>
+        <v>661.29</v>
       </c>
     </row>
     <row r="1509">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="C1509" t="n">
-        <v>122.1497908717157</v>
+        <v>651.72</v>
       </c>
     </row>
     <row r="1510">
@@ -17094,7 +17094,7 @@
         </is>
       </c>
       <c r="C1510" t="n">
-        <v>355.8507542481968</v>
+        <v>702.1</v>
       </c>
     </row>
     <row r="1511">
@@ -17105,7 +17105,7 @@
         </is>
       </c>
       <c r="C1511" t="n">
-        <v>479.0342198941556</v>
+        <v>810.23</v>
       </c>
     </row>
     <row r="1512">
@@ -17116,7 +17116,7 @@
         </is>
       </c>
       <c r="C1512" t="n">
-        <v>392.9183030848466</v>
+        <v>853.66</v>
       </c>
     </row>
     <row r="1513">
@@ -17127,7 +17127,7 @@
         </is>
       </c>
       <c r="C1513" t="n">
-        <v>483.1289242048372</v>
+        <v>791.4400000000001</v>
       </c>
     </row>
     <row r="1514">
@@ -17138,7 +17138,7 @@
         </is>
       </c>
       <c r="C1514" t="n">
-        <v>821.0529677551882</v>
+        <v>1124.29</v>
       </c>
     </row>
     <row r="1515">
@@ -17149,7 +17149,7 @@
         </is>
       </c>
       <c r="C1515" t="n">
-        <v>1121.092902248794</v>
+        <v>1570.95</v>
       </c>
     </row>
     <row r="1516">
@@ -17160,7 +17160,7 @@
         </is>
       </c>
       <c r="C1516" t="n">
-        <v>1272.30414277296</v>
+        <v>1624.96</v>
       </c>
     </row>
     <row r="1517">
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="C1517" t="n">
-        <v>1132.51331824833</v>
+        <v>1400.43</v>
       </c>
     </row>
     <row r="1518">
@@ -17182,7 +17182,7 @@
         </is>
       </c>
       <c r="C1518" t="n">
-        <v>1099.176711618483</v>
+        <v>1329.17</v>
       </c>
     </row>
     <row r="1519">
@@ -17193,7 +17193,7 @@
         </is>
       </c>
       <c r="C1519" t="n">
-        <v>1255.785343778217</v>
+        <v>1300.14</v>
       </c>
     </row>
     <row r="1520">
@@ -17204,7 +17204,7 @@
         </is>
       </c>
       <c r="C1520" t="n">
-        <v>1230.631479972018</v>
+        <v>1308.55</v>
       </c>
     </row>
     <row r="1521">
@@ -17215,7 +17215,7 @@
         </is>
       </c>
       <c r="C1521" t="n">
-        <v>1033.849037240415</v>
+        <v>1302.59</v>
       </c>
     </row>
     <row r="1522">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="C1522" t="n">
-        <v>1061.566852524872</v>
+        <v>1291.33</v>
       </c>
     </row>
     <row r="1523">
@@ -17237,7 +17237,7 @@
         </is>
       </c>
       <c r="C1523" t="n">
-        <v>1108.785935153155</v>
+        <v>1303.03</v>
       </c>
     </row>
     <row r="1524">
@@ -17248,7 +17248,7 @@
         </is>
       </c>
       <c r="C1524" t="n">
-        <v>996.1739485548776</v>
+        <v>1307.53</v>
       </c>
     </row>
     <row r="1525">
@@ -17259,7 +17259,7 @@
         </is>
       </c>
       <c r="C1525" t="n">
-        <v>1074.773226183637</v>
+        <v>1330.78</v>
       </c>
     </row>
     <row r="1526">
@@ -17270,7 +17270,7 @@
         </is>
       </c>
       <c r="C1526" t="n">
-        <v>1020.69360932133</v>
+        <v>1349.57</v>
       </c>
     </row>
     <row r="1527">
@@ -17281,7 +17281,7 @@
         </is>
       </c>
       <c r="C1527" t="n">
-        <v>1032.985816436314</v>
+        <v>1363.22</v>
       </c>
     </row>
     <row r="1528">
@@ -17292,7 +17292,7 @@
         </is>
       </c>
       <c r="C1528" t="n">
-        <v>1022.745246632344</v>
+        <v>1349.78</v>
       </c>
     </row>
     <row r="1529">
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="C1529" t="n">
-        <v>1036.572015607018</v>
+        <v>1321.52</v>
       </c>
     </row>
     <row r="1530">
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="C1530" t="n">
-        <v>1043.20876948918</v>
+        <v>1350.91</v>
       </c>
     </row>
     <row r="1531">
@@ -17325,7 +17325,7 @@
         </is>
       </c>
       <c r="C1531" t="n">
-        <v>1047.848640827272</v>
+        <v>1384.01</v>
       </c>
     </row>
     <row r="1532">
@@ -17336,7 +17336,7 @@
         </is>
       </c>
       <c r="C1532" t="n">
-        <v>1060.551746758549</v>
+        <v>1358.47</v>
       </c>
     </row>
     <row r="1533">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="C1533" t="n">
-        <v>1089.886970245726</v>
+        <v>1345.26</v>
       </c>
     </row>
     <row r="1534">
@@ -17358,7 +17358,7 @@
         </is>
       </c>
       <c r="C1534" t="n">
-        <v>1144.22940998937</v>
+        <v>1369.83</v>
       </c>
     </row>
     <row r="1535">
@@ -17369,7 +17369,7 @@
         </is>
       </c>
       <c r="C1535" t="n">
-        <v>1131.451075769594</v>
+        <v>1421.67</v>
       </c>
     </row>
     <row r="1536">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="C1536" t="n">
-        <v>1135.470075663369</v>
+        <v>1422.21</v>
       </c>
     </row>
     <row r="1537">
@@ -17391,7 +17391,7 @@
         </is>
       </c>
       <c r="C1537" t="n">
-        <v>1130.27599085811</v>
+        <v>1383.64</v>
       </c>
     </row>
   </sheetData>
